--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107321</v>
+        <v>130107316</v>
       </c>
       <c r="B2" t="n">
-        <v>80200</v>
+        <v>97702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507522</v>
+        <v>507075</v>
       </c>
       <c r="R2" t="n">
-        <v>7032834</v>
+        <v>7033179</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +752,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -768,27 +764,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130108125</v>
+        <v>130107321</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,31 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506976</v>
+        <v>507522</v>
       </c>
       <c r="R3" t="n">
-        <v>7032983</v>
+        <v>7032834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +860,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,32 +869,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107338</v>
+        <v>130108125</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,34 +924,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507073</v>
+        <v>506976</v>
       </c>
       <c r="R4" t="n">
-        <v>7032765</v>
+        <v>7032983</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +996,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,6 +1007,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1043,49 +1048,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107316</v>
+        <v>130107338</v>
       </c>
       <c r="B5" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507075</v>
+        <v>507073</v>
       </c>
       <c r="R5" t="n">
-        <v>7033179</v>
+        <v>7032765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,20 +1121,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130108117</v>
+        <v>130107322</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,31 +1161,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507057</v>
+        <v>507355</v>
       </c>
       <c r="R6" t="n">
-        <v>7032982</v>
+        <v>7032906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1228,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,27 +1237,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1280,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107322</v>
+        <v>130107354</v>
       </c>
       <c r="B7" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,37 +1292,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507355</v>
+        <v>507440</v>
       </c>
       <c r="R7" t="n">
-        <v>7032906</v>
+        <v>7032815</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1356,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,34 +1365,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1411,7 +1383,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107354</v>
+        <v>130107360</v>
       </c>
       <c r="B8" t="n">
         <v>79095</v>
@@ -1440,16 +1412,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507440</v>
+        <v>507211</v>
       </c>
       <c r="R8" t="n">
-        <v>7032815</v>
+        <v>7032876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,8 +1470,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1513,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107360</v>
+        <v>130107371</v>
       </c>
       <c r="B9" t="n">
         <v>79095</v>
@@ -1542,19 +1543,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507211</v>
+        <v>507222</v>
       </c>
       <c r="R9" t="n">
-        <v>7032876</v>
+        <v>7033039</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,34 +1598,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1644,7 +1616,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107371</v>
+        <v>130107341</v>
       </c>
       <c r="B10" t="n">
         <v>79095</v>
@@ -1679,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507222</v>
+        <v>507330</v>
       </c>
       <c r="R10" t="n">
-        <v>7033039</v>
+        <v>7032840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107341</v>
+        <v>130108117</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,34 +1729,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507330</v>
+        <v>507057</v>
       </c>
       <c r="R11" t="n">
-        <v>7032840</v>
+        <v>7032982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,7 +1801,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,6 +1812,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -3569,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107366</v>
+        <v>130108127</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,34 +3580,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507149</v>
+        <v>507051</v>
       </c>
       <c r="R27" t="n">
-        <v>7033155</v>
+        <v>7032835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,19 +3645,35 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3671,37 +3690,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130108115</v>
+        <v>130107326</v>
       </c>
       <c r="B28" t="n">
-        <v>83073</v>
+        <v>80236</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3709,10 +3732,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506966</v>
+        <v>507353</v>
       </c>
       <c r="R28" t="n">
-        <v>7032974</v>
+        <v>7032907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3747,6 +3770,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3757,19 +3785,29 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3787,10 +3825,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130108126</v>
+        <v>130107366</v>
       </c>
       <c r="B29" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,50 +3836,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507059</v>
+        <v>507149</v>
       </c>
       <c r="R29" t="n">
-        <v>7032796</v>
+        <v>7033155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3876,6 +3898,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3884,11 +3911,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3905,10 +3927,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130108127</v>
+        <v>130108115</v>
       </c>
       <c r="B30" t="n">
-        <v>80200</v>
+        <v>83073</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,21 +3938,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3943,10 +3965,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507051</v>
+        <v>506966</v>
       </c>
       <c r="R30" t="n">
-        <v>7032835</v>
+        <v>7032974</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3991,24 +4013,19 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4026,52 +4043,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107326</v>
+        <v>130108126</v>
       </c>
       <c r="B31" t="n">
-        <v>80236</v>
+        <v>57900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507353</v>
+        <v>507059</v>
       </c>
       <c r="R31" t="n">
-        <v>7032907</v>
+        <v>7032796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,44 +4132,18 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -8810,45 +8810,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130107351</v>
+        <v>130107314</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507466</v>
+        <v>507176</v>
       </c>
       <c r="R72" t="n">
-        <v>7032900</v>
+        <v>7032962</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8883,19 +8887,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8912,45 +8917,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130107340</v>
+        <v>130107315</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507241</v>
+        <v>507217</v>
       </c>
       <c r="R73" t="n">
-        <v>7032773</v>
+        <v>7033002</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8985,19 +8994,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9014,10 +9024,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130108123</v>
+        <v>130107351</v>
       </c>
       <c r="B74" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9025,42 +9035,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506984</v>
+        <v>507466</v>
       </c>
       <c r="R74" t="n">
-        <v>7032983</v>
+        <v>7032900</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9097,7 +9099,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9108,26 +9110,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9144,49 +9126,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130107314</v>
+        <v>130107340</v>
       </c>
       <c r="B75" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507176</v>
+        <v>507241</v>
       </c>
       <c r="R75" t="n">
-        <v>7032962</v>
+        <v>7032773</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9221,20 +9199,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9251,38 +9228,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130107315</v>
+        <v>130108123</v>
       </c>
       <c r="B76" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9290,10 +9271,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507217</v>
+        <v>506984</v>
       </c>
       <c r="R76" t="n">
-        <v>7033002</v>
+        <v>7032983</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9328,19 +9309,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107355</v>
+        <v>130107307</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,34 +2983,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507422</v>
+        <v>507225</v>
       </c>
       <c r="R22" t="n">
-        <v>7032836</v>
+        <v>7033149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3059,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,6 +3070,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3074,45 +3111,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107356</v>
+        <v>130107328</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>57845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507326</v>
+        <v>507190</v>
       </c>
       <c r="R23" t="n">
-        <v>7032797</v>
+        <v>7033178</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,7 +3202,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,6 +3213,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3176,7 +3234,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107361</v>
+        <v>130107355</v>
       </c>
       <c r="B24" t="n">
         <v>79095</v>
@@ -3205,19 +3263,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507236</v>
+        <v>507422</v>
       </c>
       <c r="R24" t="n">
-        <v>7032990</v>
+        <v>7032836</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,7 +3309,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,34 +3318,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3307,10 +3336,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107307</v>
+        <v>130107356</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,46 +3347,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507225</v>
+        <v>507326</v>
       </c>
       <c r="R25" t="n">
-        <v>7033149</v>
+        <v>7032797</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3411,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3405,31 +3422,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3446,61 +3438,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107328</v>
+        <v>130107361</v>
       </c>
       <c r="B26" t="n">
-        <v>57845</v>
+        <v>79095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507190</v>
+        <v>507236</v>
       </c>
       <c r="R26" t="n">
-        <v>7033178</v>
+        <v>7032990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3516,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,12 +3525,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130108127</v>
+        <v>130107366</v>
       </c>
       <c r="B27" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,37 +3580,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507051</v>
+        <v>507149</v>
       </c>
       <c r="R27" t="n">
-        <v>7032835</v>
+        <v>7033155</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3645,35 +3642,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3690,41 +3671,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107326</v>
+        <v>130108115</v>
       </c>
       <c r="B28" t="n">
-        <v>80236</v>
+        <v>83073</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3732,10 +3709,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507353</v>
+        <v>506966</v>
       </c>
       <c r="R28" t="n">
-        <v>7032907</v>
+        <v>7032974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3770,11 +3747,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3785,29 +3757,19 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3825,10 +3787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,34 +3798,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R29" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3898,11 +3876,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3911,6 +3884,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3927,10 +3905,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130108115</v>
+        <v>130108127</v>
       </c>
       <c r="B30" t="n">
-        <v>83073</v>
+        <v>80200</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,21 +3916,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,10 +3943,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506966</v>
+        <v>507051</v>
       </c>
       <c r="R30" t="n">
-        <v>7032974</v>
+        <v>7032835</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4013,19 +3991,24 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4043,61 +4026,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130108126</v>
+        <v>130107326</v>
       </c>
       <c r="B31" t="n">
-        <v>57900</v>
+        <v>80236</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507059</v>
+        <v>507353</v>
       </c>
       <c r="R31" t="n">
-        <v>7032796</v>
+        <v>7032907</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,18 +4106,44 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107329</v>
+        <v>130107343</v>
       </c>
       <c r="B39" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,41 +4996,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507152</v>
+        <v>507356</v>
       </c>
       <c r="R39" t="n">
-        <v>7033148</v>
+        <v>7032842</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5067,7 +5060,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5076,34 +5069,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5120,10 +5087,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130107343</v>
+        <v>130107329</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>91635</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5131,34 +5098,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507356</v>
+        <v>507152</v>
       </c>
       <c r="R40" t="n">
-        <v>7032842</v>
+        <v>7033148</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5195,7 +5169,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,8 +5178,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5891,41 +5891,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107327</v>
+        <v>130107310</v>
       </c>
       <c r="B47" t="n">
-        <v>80236</v>
+        <v>57738</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5933,10 +5930,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507239</v>
+        <v>507084</v>
       </c>
       <c r="R47" t="n">
-        <v>7032943</v>
+        <v>7033149</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5973,7 +5970,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5982,7 +5979,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5993,17 +5989,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6327,10 +6328,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107310</v>
+        <v>130108128</v>
       </c>
       <c r="B51" t="n">
-        <v>57738</v>
+        <v>78107</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6338,27 +6339,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507084</v>
+        <v>507058</v>
       </c>
       <c r="R51" t="n">
-        <v>7033149</v>
+        <v>7032972</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6404,25 +6404,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ51" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6433,14 +6424,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6565,37 +6551,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130108128</v>
+        <v>130107327</v>
       </c>
       <c r="B53" t="n">
-        <v>78107</v>
+        <v>80236</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6603,10 +6593,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507058</v>
+        <v>507239</v>
       </c>
       <c r="R53" t="n">
-        <v>7032972</v>
+        <v>7032943</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6641,6 +6631,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6651,19 +6646,24 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6811,45 +6811,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107358</v>
+        <v>130107318</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507233</v>
+        <v>507226</v>
       </c>
       <c r="R55" t="n">
-        <v>7032821</v>
+        <v>7033130</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6884,19 +6888,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6913,7 +6918,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130107336</v>
+        <v>130107358</v>
       </c>
       <c r="B56" t="n">
         <v>79095</v>
@@ -6948,10 +6953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507081</v>
+        <v>507233</v>
       </c>
       <c r="R56" t="n">
-        <v>7032660</v>
+        <v>7032821</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6988,7 +6993,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7015,7 +7020,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130107352</v>
+        <v>130107336</v>
       </c>
       <c r="B57" t="n">
         <v>79095</v>
@@ -7050,10 +7055,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507537</v>
+        <v>507081</v>
       </c>
       <c r="R57" t="n">
-        <v>7032882</v>
+        <v>7032660</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7090,7 +7095,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7117,10 +7122,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130108116</v>
+        <v>130107352</v>
       </c>
       <c r="B58" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,37 +7133,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506959</v>
+        <v>507537</v>
       </c>
       <c r="R58" t="n">
-        <v>7032984</v>
+        <v>7032882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7193,30 +7195,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7233,10 +7224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130108124</v>
+        <v>130108116</v>
       </c>
       <c r="B59" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7244,31 +7235,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7276,10 +7262,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506973</v>
+        <v>506959</v>
       </c>
       <c r="R59" t="n">
-        <v>7032980</v>
+        <v>7032984</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7314,24 +7300,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -7363,38 +7340,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130107318</v>
+        <v>130108124</v>
       </c>
       <c r="B60" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7402,10 +7383,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507226</v>
+        <v>506973</v>
       </c>
       <c r="R60" t="n">
-        <v>7033130</v>
+        <v>7032980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7440,19 +7421,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7470,10 +7470,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130107367</v>
+        <v>130107325</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7481,34 +7481,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507157</v>
+        <v>507225</v>
       </c>
       <c r="R61" t="n">
-        <v>7033174</v>
+        <v>7033115</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,7 +7548,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7554,8 +7557,34 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7572,10 +7601,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107330</v>
+        <v>130107367</v>
       </c>
       <c r="B62" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,37 +7612,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507223</v>
+        <v>507157</v>
       </c>
       <c r="R62" t="n">
-        <v>7032791</v>
+        <v>7033174</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7650,7 +7676,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7659,34 +7685,8 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7703,10 +7703,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130107335</v>
+        <v>130107330</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>91659</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7714,34 +7714,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507088</v>
+        <v>507223</v>
       </c>
       <c r="R63" t="n">
-        <v>7032634</v>
+        <v>7032791</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7778,7 +7781,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7787,8 +7790,34 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7805,10 +7834,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130107325</v>
+        <v>130107335</v>
       </c>
       <c r="B64" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7816,37 +7845,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507225</v>
+        <v>507088</v>
       </c>
       <c r="R64" t="n">
-        <v>7033115</v>
+        <v>7032634</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7883,7 +7909,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7892,34 +7918,8 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8201,10 +8201,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130107337</v>
+        <v>130107306</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,34 +8212,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507084</v>
+        <v>507221</v>
       </c>
       <c r="R67" t="n">
-        <v>7032690</v>
+        <v>7033159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8276,7 +8288,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8287,6 +8299,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8303,10 +8340,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130107372</v>
+        <v>130107302</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8314,34 +8351,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507223</v>
+        <v>507075</v>
       </c>
       <c r="R68" t="n">
-        <v>7033198</v>
+        <v>7032759</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8378,7 +8423,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8389,6 +8434,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8405,7 +8475,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130107344</v>
+        <v>130107337</v>
       </c>
       <c r="B69" t="n">
         <v>79095</v>
@@ -8434,19 +8504,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507358</v>
+        <v>507084</v>
       </c>
       <c r="R69" t="n">
-        <v>7032855</v>
+        <v>7032690</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8483,7 +8550,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8492,34 +8559,8 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8536,10 +8577,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130107306</v>
+        <v>130107372</v>
       </c>
       <c r="B70" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8547,46 +8588,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507221</v>
+        <v>507223</v>
       </c>
       <c r="R70" t="n">
-        <v>7033159</v>
+        <v>7033198</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8623,7 +8652,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8634,31 +8663,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8675,10 +8679,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130107302</v>
+        <v>130107344</v>
       </c>
       <c r="B71" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8686,31 +8690,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8718,10 +8717,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507075</v>
+        <v>507358</v>
       </c>
       <c r="R71" t="n">
-        <v>7032759</v>
+        <v>7032855</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8758,7 +8757,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
+          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8767,6 +8766,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107316</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107321</v>
+        <v>130107338</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507522</v>
+        <v>507073</v>
       </c>
       <c r="R3" t="n">
-        <v>7032834</v>
+        <v>7032765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,34 +866,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -913,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130108125</v>
+        <v>130107321</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,31 +895,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506976</v>
+        <v>507522</v>
       </c>
       <c r="R4" t="n">
-        <v>7032983</v>
+        <v>7032834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,32 +971,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107338</v>
+        <v>130108125</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,34 +1026,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507073</v>
+        <v>506976</v>
       </c>
       <c r="R5" t="n">
-        <v>7032765</v>
+        <v>7032983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,6 +1109,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -2215,10 +2215,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107323</v>
+        <v>130107369</v>
       </c>
       <c r="B15" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,37 +2226,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507416</v>
+        <v>507237</v>
       </c>
       <c r="R15" t="n">
-        <v>7032925</v>
+        <v>7033036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2290,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,34 +2299,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2346,7 +2317,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107369</v>
+        <v>130107363</v>
       </c>
       <c r="B16" t="n">
         <v>79095</v>
@@ -2381,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507237</v>
+        <v>507069</v>
       </c>
       <c r="R16" t="n">
-        <v>7033036</v>
+        <v>7033199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,7 +2419,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107363</v>
+        <v>130108131</v>
       </c>
       <c r="B17" t="n">
         <v>79095</v>
@@ -2477,16 +2448,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507069</v>
+        <v>506958</v>
       </c>
       <c r="R17" t="n">
-        <v>7033199</v>
+        <v>7032984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2521,19 +2495,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2550,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108131</v>
+        <v>130107323</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,21 +2546,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2588,10 +2573,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506958</v>
+        <v>507416</v>
       </c>
       <c r="R18" t="n">
-        <v>7032984</v>
+        <v>7032925</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,6 +2611,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2636,19 +2626,29 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107307</v>
+        <v>130107355</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,46 +2983,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507225</v>
+        <v>507422</v>
       </c>
       <c r="R22" t="n">
-        <v>7033149</v>
+        <v>7032836</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3047,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,31 +3058,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3111,61 +3074,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107328</v>
+        <v>130107356</v>
       </c>
       <c r="B23" t="n">
-        <v>57845</v>
+        <v>79095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507190</v>
+        <v>507326</v>
       </c>
       <c r="R23" t="n">
-        <v>7033178</v>
+        <v>7032797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3202,7 +3149,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,11 +3160,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3234,7 +3176,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107355</v>
+        <v>130107361</v>
       </c>
       <c r="B24" t="n">
         <v>79095</v>
@@ -3263,16 +3205,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507422</v>
+        <v>507236</v>
       </c>
       <c r="R24" t="n">
-        <v>7032836</v>
+        <v>7032990</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3309,7 +3254,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,8 +3263,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3336,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107356</v>
+        <v>130107307</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,34 +3318,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507326</v>
+        <v>507225</v>
       </c>
       <c r="R25" t="n">
-        <v>7032797</v>
+        <v>7033149</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3411,7 +3394,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,6 +3405,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3438,48 +3446,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107361</v>
+        <v>130107328</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>57845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507236</v>
+        <v>507190</v>
       </c>
       <c r="R26" t="n">
-        <v>7032990</v>
+        <v>7033178</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3537,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3525,33 +3546,12 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130108126</v>
+        <v>130108127</v>
       </c>
       <c r="B29" t="n">
-        <v>57900</v>
+        <v>80200</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,50 +3798,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507059</v>
+        <v>507051</v>
       </c>
       <c r="R29" t="n">
-        <v>7032796</v>
+        <v>7032835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3882,12 +3869,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3905,37 +3908,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130108127</v>
+        <v>130107326</v>
       </c>
       <c r="B30" t="n">
-        <v>80200</v>
+        <v>80236</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3943,10 +3950,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507051</v>
+        <v>507353</v>
       </c>
       <c r="R30" t="n">
-        <v>7032835</v>
+        <v>7032907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3981,6 +3988,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4006,9 +4018,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4026,52 +4043,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107326</v>
+        <v>130108126</v>
       </c>
       <c r="B31" t="n">
-        <v>80236</v>
+        <v>57900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507353</v>
+        <v>507059</v>
       </c>
       <c r="R31" t="n">
-        <v>7032907</v>
+        <v>7032796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,44 +4132,18 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4881,7 +4881,7 @@
         <v>130107317</v>
       </c>
       <c r="B38" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,10 +4985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107343</v>
+        <v>130107329</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>91637</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,34 +4996,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507356</v>
+        <v>507152</v>
       </c>
       <c r="R39" t="n">
-        <v>7032842</v>
+        <v>7033148</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5060,7 +5067,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,8 +5076,34 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5087,10 +5120,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130107329</v>
+        <v>130107343</v>
       </c>
       <c r="B40" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5098,41 +5131,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507152</v>
+        <v>507356</v>
       </c>
       <c r="R40" t="n">
-        <v>7033148</v>
+        <v>7032842</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5169,7 +5195,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5178,34 +5204,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5222,45 +5222,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107342</v>
+        <v>130107311</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507376</v>
+        <v>507355</v>
       </c>
       <c r="R41" t="n">
-        <v>7032813</v>
+        <v>7032851</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5295,19 +5299,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5324,7 +5329,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107357</v>
+        <v>130107342</v>
       </c>
       <c r="B42" t="n">
         <v>79095</v>
@@ -5359,10 +5364,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507283</v>
+        <v>507376</v>
       </c>
       <c r="R42" t="n">
-        <v>7032795</v>
+        <v>7032813</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5426,7 +5431,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130107364</v>
+        <v>130107357</v>
       </c>
       <c r="B43" t="n">
         <v>79095</v>
@@ -5461,10 +5466,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507091</v>
+        <v>507283</v>
       </c>
       <c r="R43" t="n">
-        <v>7033218</v>
+        <v>7032795</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5501,7 +5506,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5528,49 +5533,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107311</v>
+        <v>130107364</v>
       </c>
       <c r="B44" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507355</v>
+        <v>507091</v>
       </c>
       <c r="R44" t="n">
-        <v>7032851</v>
+        <v>7033218</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,20 +5606,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,26 +5646,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5673,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R45" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5711,6 +5715,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5728,17 +5737,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5756,10 +5770,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B46" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5767,30 +5781,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5798,10 +5808,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R46" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5836,11 +5846,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5858,22 +5863,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107310</v>
+        <v>130107362</v>
       </c>
       <c r="B47" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5902,38 +5902,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507084</v>
+        <v>507201</v>
       </c>
       <c r="R47" t="n">
-        <v>7033149</v>
+        <v>7032984</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5970,7 +5966,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5981,31 +5977,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6022,45 +5993,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107362</v>
+        <v>130107327</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>80236</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507201</v>
+        <v>507239</v>
       </c>
       <c r="R48" t="n">
-        <v>7032984</v>
+        <v>7032943</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6097,7 +6075,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6106,8 +6084,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6328,37 +6327,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130108128</v>
+        <v>130107312</v>
       </c>
       <c r="B51" t="n">
-        <v>78107</v>
+        <v>97704</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507058</v>
+        <v>507337</v>
       </c>
       <c r="R51" t="n">
-        <v>7032972</v>
+        <v>7032943</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6414,19 +6414,9 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6444,38 +6434,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107312</v>
+        <v>130107310</v>
       </c>
       <c r="B52" t="n">
-        <v>97702</v>
+        <v>57738</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6483,10 +6473,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507337</v>
+        <v>507084</v>
       </c>
       <c r="R52" t="n">
-        <v>7032943</v>
+        <v>7033149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6521,19 +6511,43 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6551,41 +6565,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130107327</v>
+        <v>130108128</v>
       </c>
       <c r="B53" t="n">
-        <v>80236</v>
+        <v>78107</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6593,10 +6603,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507239</v>
+        <v>507058</v>
       </c>
       <c r="R53" t="n">
-        <v>7032943</v>
+        <v>7032972</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6631,11 +6641,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6646,24 +6651,19 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6811,49 +6811,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107318</v>
+        <v>130107336</v>
       </c>
       <c r="B55" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507226</v>
+        <v>507081</v>
       </c>
       <c r="R55" t="n">
-        <v>7033130</v>
+        <v>7032660</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6888,20 +6884,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6918,7 +6913,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130107358</v>
+        <v>130107352</v>
       </c>
       <c r="B56" t="n">
         <v>79095</v>
@@ -6953,10 +6948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507233</v>
+        <v>507537</v>
       </c>
       <c r="R56" t="n">
-        <v>7032821</v>
+        <v>7032882</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7020,10 +7015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130107336</v>
+        <v>130108124</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7031,34 +7026,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507081</v>
+        <v>506973</v>
       </c>
       <c r="R57" t="n">
-        <v>7032660</v>
+        <v>7032980</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7095,7 +7098,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7106,6 +7109,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7122,45 +7145,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130107352</v>
+        <v>130107318</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507537</v>
+        <v>507226</v>
       </c>
       <c r="R58" t="n">
-        <v>7032882</v>
+        <v>7033130</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7195,19 +7222,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7224,10 +7252,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130108116</v>
+        <v>130107358</v>
       </c>
       <c r="B59" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7235,37 +7263,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506959</v>
+        <v>507233</v>
       </c>
       <c r="R59" t="n">
-        <v>7032984</v>
+        <v>7032821</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7300,30 +7325,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7340,10 +7354,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130108124</v>
+        <v>130108116</v>
       </c>
       <c r="B60" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7351,31 +7365,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7383,10 +7392,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506973</v>
+        <v>506959</v>
       </c>
       <c r="R60" t="n">
-        <v>7032980</v>
+        <v>7032984</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7421,24 +7430,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130107325</v>
+        <v>130107335</v>
       </c>
       <c r="B61" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7481,37 +7481,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507225</v>
+        <v>507088</v>
       </c>
       <c r="R61" t="n">
-        <v>7033115</v>
+        <v>7032634</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7548,7 +7545,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7557,34 +7554,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7601,10 +7572,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107367</v>
+        <v>130107330</v>
       </c>
       <c r="B62" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7612,34 +7583,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507157</v>
+        <v>507223</v>
       </c>
       <c r="R62" t="n">
-        <v>7033174</v>
+        <v>7032791</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7676,7 +7650,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7685,8 +7659,34 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7703,10 +7703,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130107330</v>
+        <v>130107303</v>
       </c>
       <c r="B63" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7714,24 +7714,29 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7741,10 +7746,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507223</v>
+        <v>507345</v>
       </c>
       <c r="R63" t="n">
-        <v>7032791</v>
+        <v>7032953</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7781,7 +7786,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7790,7 +7795,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7834,10 +7838,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130107335</v>
+        <v>130108118</v>
       </c>
       <c r="B64" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7845,34 +7849,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507088</v>
+        <v>506992</v>
       </c>
       <c r="R64" t="n">
-        <v>7032634</v>
+        <v>7032926</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,7 +7921,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7920,6 +7932,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7936,10 +7968,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130108118</v>
+        <v>130107367</v>
       </c>
       <c r="B65" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7947,42 +7979,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506992</v>
+        <v>507157</v>
       </c>
       <c r="R65" t="n">
-        <v>7032926</v>
+        <v>7033174</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8019,7 +8043,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8030,26 +8054,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8066,10 +8070,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130107303</v>
+        <v>130107325</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8077,31 +8081,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8109,10 +8108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507345</v>
+        <v>507225</v>
       </c>
       <c r="R66" t="n">
-        <v>7032953</v>
+        <v>7033115</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8149,7 +8148,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8158,6 +8157,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8168,22 +8168,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8810,38 +8810,42 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130107314</v>
+        <v>130108123</v>
       </c>
       <c r="B72" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8849,10 +8853,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507176</v>
+        <v>506984</v>
       </c>
       <c r="R72" t="n">
-        <v>7032962</v>
+        <v>7032983</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8887,19 +8891,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8917,10 +8940,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130107315</v>
+        <v>130107314</v>
       </c>
       <c r="B73" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8956,10 +8979,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507217</v>
+        <v>507176</v>
       </c>
       <c r="R73" t="n">
-        <v>7033002</v>
+        <v>7032962</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9024,45 +9047,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130107351</v>
+        <v>130107315</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507466</v>
+        <v>507217</v>
       </c>
       <c r="R74" t="n">
-        <v>7032900</v>
+        <v>7033002</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9097,19 +9124,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9126,7 +9154,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130107340</v>
+        <v>130107351</v>
       </c>
       <c r="B75" t="n">
         <v>79095</v>
@@ -9161,10 +9189,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507241</v>
+        <v>507466</v>
       </c>
       <c r="R75" t="n">
-        <v>7032773</v>
+        <v>7032900</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9201,7 +9229,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9228,10 +9256,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130108123</v>
+        <v>130107340</v>
       </c>
       <c r="B76" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9239,42 +9267,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506984</v>
+        <v>507241</v>
       </c>
       <c r="R76" t="n">
-        <v>7032983</v>
+        <v>7032773</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9311,7 +9331,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9322,26 +9342,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9358,10 +9358,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130107331</v>
+        <v>130107333</v>
       </c>
       <c r="B77" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9369,37 +9369,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507157</v>
+        <v>507097</v>
       </c>
       <c r="R77" t="n">
-        <v>7033090</v>
+        <v>7032620</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9436,7 +9433,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9445,34 +9442,8 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9489,10 +9460,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130107333</v>
+        <v>130107331</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9500,34 +9471,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507097</v>
+        <v>507157</v>
       </c>
       <c r="R78" t="n">
-        <v>7032620</v>
+        <v>7033090</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9564,7 +9538,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9573,8 +9547,34 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -10146,7 +10146,7 @@
         <v>130107313</v>
       </c>
       <c r="B84" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10250,52 +10250,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130107309</v>
+        <v>130107349</v>
       </c>
       <c r="B85" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>507227</v>
+        <v>507397</v>
       </c>
       <c r="R85" t="n">
-        <v>7032981</v>
+        <v>7032912</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10332,7 +10325,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På en sälg i granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10341,34 +10334,8 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10385,45 +10352,52 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130107349</v>
+        <v>130107309</v>
       </c>
       <c r="B86" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>507397</v>
+        <v>507227</v>
       </c>
       <c r="R86" t="n">
-        <v>7032912</v>
+        <v>7032981</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10460,7 +10434,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en sälg i granskog.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10469,8 +10443,34 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10838,7 +10838,7 @@
         <v>130107319</v>
       </c>
       <c r="B90" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107316</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107338</v>
+        <v>130108125</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507073</v>
+        <v>506976</v>
       </c>
       <c r="R3" t="n">
-        <v>7032765</v>
+        <v>7032983</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,6 +876,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107321</v>
+        <v>130107338</v>
       </c>
       <c r="B4" t="n">
-        <v>80200</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +928,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507522</v>
+        <v>507073</v>
       </c>
       <c r="R4" t="n">
-        <v>7032834</v>
+        <v>7032765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,7 +992,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,34 +1001,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1015,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130108125</v>
+        <v>130107321</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,31 +1030,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506976</v>
+        <v>507522</v>
       </c>
       <c r="R5" t="n">
-        <v>7032983</v>
+        <v>7032834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1097,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,32 +1106,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
         <v>130107322</v>
       </c>
       <c r="B6" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>130107354</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107360</v>
+        <v>130108117</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,26 +1394,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1421,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507211</v>
+        <v>507057</v>
       </c>
       <c r="R8" t="n">
-        <v>7032876</v>
+        <v>7032982</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1466,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,13 +1475,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1489,14 +1493,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1514,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107371</v>
+        <v>130107360</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,16 +1542,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507222</v>
+        <v>507211</v>
       </c>
       <c r="R9" t="n">
-        <v>7033039</v>
+        <v>7032876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1591,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,8 +1600,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,10 +1644,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107341</v>
+        <v>130107371</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507330</v>
+        <v>507222</v>
       </c>
       <c r="R10" t="n">
-        <v>7032840</v>
+        <v>7033039</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130108117</v>
+        <v>130107341</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,42 +1757,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507057</v>
+        <v>507330</v>
       </c>
       <c r="R11" t="n">
-        <v>7032982</v>
+        <v>7032840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1821,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,26 +1832,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1851,7 +1851,7 @@
         <v>130107373</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>130107304</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>130108119</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107369</v>
+        <v>130107353</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507237</v>
+        <v>507521</v>
       </c>
       <c r="R15" t="n">
-        <v>7033036</v>
+        <v>7032767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2320,7 +2320,7 @@
         <v>130107363</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130108131</v>
+        <v>130107323</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>80285</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506958</v>
+        <v>507416</v>
       </c>
       <c r="R17" t="n">
-        <v>7032984</v>
+        <v>7032925</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,6 +2495,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2505,19 +2510,29 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2535,10 +2550,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130107323</v>
+        <v>130107369</v>
       </c>
       <c r="B18" t="n">
-        <v>80200</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2546,37 +2561,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507416</v>
+        <v>507237</v>
       </c>
       <c r="R18" t="n">
-        <v>7032925</v>
+        <v>7033036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2625,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,34 +2634,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2666,10 +2652,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130107374</v>
+        <v>130108131</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,16 +2681,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507101</v>
+        <v>506958</v>
       </c>
       <c r="R19" t="n">
-        <v>7033240</v>
+        <v>7032984</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,19 +2728,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2768,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107353</v>
+        <v>130107374</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507521</v>
+        <v>507101</v>
       </c>
       <c r="R20" t="n">
-        <v>7032767</v>
+        <v>7033240</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,7 +2873,7 @@
         <v>130107345</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107355</v>
+        <v>130107361</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,16 +3001,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507422</v>
+        <v>507236</v>
       </c>
       <c r="R22" t="n">
-        <v>7032836</v>
+        <v>7032990</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3050,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,8 +3059,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3074,45 +3103,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107356</v>
+        <v>130107328</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>57930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507326</v>
+        <v>507190</v>
       </c>
       <c r="R23" t="n">
-        <v>7032797</v>
+        <v>7033178</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,7 +3194,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,6 +3205,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3176,10 +3226,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107361</v>
+        <v>130107355</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3205,19 +3255,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507236</v>
+        <v>507422</v>
       </c>
       <c r="R24" t="n">
-        <v>7032990</v>
+        <v>7032836</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,7 +3301,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,34 +3310,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3307,10 +3328,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107307</v>
+        <v>130107356</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,46 +3339,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507225</v>
+        <v>507326</v>
       </c>
       <c r="R25" t="n">
-        <v>7033149</v>
+        <v>7032797</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3403,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3405,31 +3414,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3446,27 +3430,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107328</v>
+        <v>130107307</v>
       </c>
       <c r="B26" t="n">
-        <v>57845</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3474,16 +3458,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3497,10 +3477,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507190</v>
+        <v>507225</v>
       </c>
       <c r="R26" t="n">
-        <v>7033178</v>
+        <v>7033149</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3517,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3552,6 +3532,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
         <v>130107366</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>130108115</v>
       </c>
       <c r="B28" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130108127</v>
+        <v>130108126</v>
       </c>
       <c r="B29" t="n">
-        <v>80200</v>
+        <v>57985</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,37 +3798,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507051</v>
+        <v>507059</v>
       </c>
       <c r="R29" t="n">
-        <v>7032835</v>
+        <v>7032796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3869,28 +3882,12 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3908,41 +3905,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107326</v>
+        <v>130108127</v>
       </c>
       <c r="B30" t="n">
-        <v>80236</v>
+        <v>80285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3950,10 +3943,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507353</v>
+        <v>507051</v>
       </c>
       <c r="R30" t="n">
-        <v>7032907</v>
+        <v>7032835</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3988,11 +3981,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4018,14 +4006,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4043,61 +4026,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130108126</v>
+        <v>130107326</v>
       </c>
       <c r="B31" t="n">
-        <v>57900</v>
+        <v>80321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507059</v>
+        <v>507353</v>
       </c>
       <c r="R31" t="n">
-        <v>7032796</v>
+        <v>7032907</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,18 +4106,44 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4164,7 +4164,7 @@
         <v>130107350</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4263,10 +4263,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130108113</v>
+        <v>130107305</v>
       </c>
       <c r="B33" t="n">
-        <v>83073</v>
+        <v>57826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4274,26 +4274,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4301,10 +4306,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507086</v>
+        <v>507427</v>
       </c>
       <c r="R33" t="n">
-        <v>7032654</v>
+        <v>7032906</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4339,16 +4344,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4359,9 +4373,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4379,10 +4398,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107305</v>
+        <v>130108113</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>83158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4390,31 +4409,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4422,10 +4436,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507427</v>
+        <v>507086</v>
       </c>
       <c r="R34" t="n">
-        <v>7032906</v>
+        <v>7032654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4460,25 +4474,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4489,14 +4494,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107339</v>
+        <v>130107332</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4543,19 +4543,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507154</v>
+        <v>507011</v>
       </c>
       <c r="R35" t="n">
-        <v>7032764</v>
+        <v>7033080</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4592,7 +4589,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På en stående död granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4601,34 +4598,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4645,45 +4616,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107332</v>
+        <v>130107317</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507011</v>
+        <v>507267</v>
       </c>
       <c r="R36" t="n">
-        <v>7033080</v>
+        <v>7033117</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4718,19 +4693,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4747,10 +4723,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107370</v>
+        <v>130107339</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4785,10 +4761,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507211</v>
+        <v>507154</v>
       </c>
       <c r="R37" t="n">
-        <v>7033009</v>
+        <v>7032764</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4825,7 +4801,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På en stående död granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,12 +4831,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4878,38 +4854,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107317</v>
+        <v>130107370</v>
       </c>
       <c r="B38" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4917,10 +4892,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507267</v>
+        <v>507211</v>
       </c>
       <c r="R38" t="n">
-        <v>7033117</v>
+        <v>7033009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4955,6 +4930,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4968,6 +4948,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107329</v>
+        <v>130107343</v>
       </c>
       <c r="B39" t="n">
-        <v>91637</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,41 +4996,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507152</v>
+        <v>507356</v>
       </c>
       <c r="R39" t="n">
-        <v>7033148</v>
+        <v>7032842</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5067,7 +5060,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5076,34 +5069,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5120,10 +5087,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130107343</v>
+        <v>130107329</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>91724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5131,34 +5098,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507356</v>
+        <v>507152</v>
       </c>
       <c r="R40" t="n">
-        <v>7032842</v>
+        <v>7033148</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5195,7 +5169,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,8 +5178,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5222,49 +5222,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107311</v>
+        <v>130107342</v>
       </c>
       <c r="B41" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507355</v>
+        <v>507376</v>
       </c>
       <c r="R41" t="n">
-        <v>7032851</v>
+        <v>7032813</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5299,20 +5295,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5329,10 +5324,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107342</v>
+        <v>130107364</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5364,10 +5359,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507376</v>
+        <v>507091</v>
       </c>
       <c r="R42" t="n">
-        <v>7032813</v>
+        <v>7033218</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5404,7 +5399,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5434,7 +5429,7 @@
         <v>130107357</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5533,45 +5528,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107364</v>
+        <v>130107311</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507091</v>
+        <v>507355</v>
       </c>
       <c r="R44" t="n">
-        <v>7033218</v>
+        <v>7032851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5606,19 +5605,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5638,7 +5638,7 @@
         <v>130107324</v>
       </c>
       <c r="B45" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>130108129</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107362</v>
+        <v>130107365</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507201</v>
+        <v>507106</v>
       </c>
       <c r="R47" t="n">
-        <v>7032984</v>
+        <v>7033205</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5993,52 +5993,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107327</v>
+        <v>130107368</v>
       </c>
       <c r="B48" t="n">
-        <v>80236</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507239</v>
+        <v>507204</v>
       </c>
       <c r="R48" t="n">
-        <v>7032943</v>
+        <v>7033154</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6075,7 +6068,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6084,29 +6077,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6123,10 +6095,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130107365</v>
+        <v>130108128</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>78192</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6134,34 +6106,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507106</v>
+        <v>507058</v>
       </c>
       <c r="R49" t="n">
-        <v>7033205</v>
+        <v>7032972</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6196,19 +6171,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6225,45 +6211,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107368</v>
+        <v>130107312</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507204</v>
+        <v>507337</v>
       </c>
       <c r="R50" t="n">
-        <v>7033154</v>
+        <v>7032943</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6298,19 +6288,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6327,49 +6318,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107312</v>
+        <v>130107362</v>
       </c>
       <c r="B51" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507337</v>
+        <v>507201</v>
       </c>
       <c r="R51" t="n">
-        <v>7032943</v>
+        <v>7032984</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6404,20 +6391,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6434,38 +6420,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107310</v>
+        <v>130107327</v>
       </c>
       <c r="B52" t="n">
-        <v>57738</v>
+        <v>80321</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6473,10 +6462,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507084</v>
+        <v>507239</v>
       </c>
       <c r="R52" t="n">
-        <v>7033149</v>
+        <v>7032943</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6513,7 +6502,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6522,6 +6511,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6532,22 +6522,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6565,10 +6550,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130108128</v>
+        <v>130107310</v>
       </c>
       <c r="B53" t="n">
-        <v>78107</v>
+        <v>57823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6576,26 +6561,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6603,10 +6589,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507058</v>
+        <v>507084</v>
       </c>
       <c r="R53" t="n">
-        <v>7032972</v>
+        <v>7033149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6641,16 +6627,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ53" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6661,9 +6656,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6684,7 +6684,7 @@
         <v>130108120</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107336</v>
+        <v>130107358</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507081</v>
+        <v>507233</v>
       </c>
       <c r="R55" t="n">
-        <v>7032660</v>
+        <v>7032821</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130107352</v>
+        <v>130107336</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507537</v>
+        <v>507081</v>
       </c>
       <c r="R56" t="n">
-        <v>7032882</v>
+        <v>7032660</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7018,7 +7018,7 @@
         <v>130108124</v>
       </c>
       <c r="B57" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>130107318</v>
       </c>
       <c r="B58" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7252,10 +7252,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130107358</v>
+        <v>130107352</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507233</v>
+        <v>507537</v>
       </c>
       <c r="R59" t="n">
-        <v>7032821</v>
+        <v>7032882</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7357,7 +7357,7 @@
         <v>130108116</v>
       </c>
       <c r="B60" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130107335</v>
+        <v>130108118</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7481,34 +7481,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507088</v>
+        <v>506992</v>
       </c>
       <c r="R61" t="n">
-        <v>7032634</v>
+        <v>7032926</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,7 +7553,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7556,6 +7564,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7572,10 +7600,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107330</v>
+        <v>130107367</v>
       </c>
       <c r="B62" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,37 +7611,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507223</v>
+        <v>507157</v>
       </c>
       <c r="R62" t="n">
-        <v>7032791</v>
+        <v>7033174</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7650,7 +7675,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7659,34 +7684,8 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7706,7 +7705,7 @@
         <v>130107303</v>
       </c>
       <c r="B63" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7838,10 +7837,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130108118</v>
+        <v>130107330</v>
       </c>
       <c r="B64" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7849,29 +7848,24 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7881,10 +7875,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506992</v>
+        <v>507223</v>
       </c>
       <c r="R64" t="n">
-        <v>7032926</v>
+        <v>7032791</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7921,7 +7915,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7930,12 +7924,13 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -7948,9 +7943,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7968,10 +7968,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130107367</v>
+        <v>130107335</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507157</v>
+        <v>507088</v>
       </c>
       <c r="R65" t="n">
-        <v>7033174</v>
+        <v>7032634</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8073,7 +8073,7 @@
         <v>130107325</v>
       </c>
       <c r="B66" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130107306</v>
+        <v>130107302</v>
       </c>
       <c r="B67" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8234,24 +8234,20 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507221</v>
+        <v>507075</v>
       </c>
       <c r="R67" t="n">
-        <v>7033159</v>
+        <v>7032759</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8288,7 +8284,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8340,10 +8336,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130107302</v>
+        <v>130107337</v>
       </c>
       <c r="B68" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8351,42 +8347,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507075</v>
+        <v>507084</v>
       </c>
       <c r="R68" t="n">
-        <v>7032759</v>
+        <v>7032690</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8423,7 +8411,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8434,31 +8422,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8475,10 +8438,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130107337</v>
+        <v>130107372</v>
       </c>
       <c r="B69" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8510,10 +8473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507084</v>
+        <v>507223</v>
       </c>
       <c r="R69" t="n">
-        <v>7032690</v>
+        <v>7033198</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8550,7 +8513,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8577,10 +8540,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130107372</v>
+        <v>130107344</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8606,16 +8569,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507223</v>
+        <v>507358</v>
       </c>
       <c r="R70" t="n">
-        <v>7033198</v>
+        <v>7032855</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8652,7 +8618,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8661,8 +8627,34 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8679,10 +8671,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130107344</v>
+        <v>130107306</v>
       </c>
       <c r="B71" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8690,37 +8682,46 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507358</v>
+        <v>507221</v>
       </c>
       <c r="R71" t="n">
-        <v>7032855</v>
+        <v>7033159</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8757,7 +8758,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8766,7 +8767,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8813,7 +8813,7 @@
         <v>130108123</v>
       </c>
       <c r="B72" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>130107314</v>
       </c>
       <c r="B73" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9047,49 +9047,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130107315</v>
+        <v>130107340</v>
       </c>
       <c r="B74" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507217</v>
+        <v>507241</v>
       </c>
       <c r="R74" t="n">
-        <v>7033002</v>
+        <v>7032773</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9124,20 +9120,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9157,7 +9152,7 @@
         <v>130107351</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9256,45 +9251,49 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130107340</v>
+        <v>130107315</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507241</v>
+        <v>507217</v>
       </c>
       <c r="R76" t="n">
-        <v>7032773</v>
+        <v>7033002</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9329,19 +9328,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9358,10 +9358,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130107333</v>
+        <v>130107331</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>91748</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9369,34 +9369,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507097</v>
+        <v>507157</v>
       </c>
       <c r="R77" t="n">
-        <v>7032620</v>
+        <v>7033090</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9433,7 +9436,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9442,8 +9445,34 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9460,10 +9489,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130107331</v>
+        <v>130107333</v>
       </c>
       <c r="B78" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9471,37 +9500,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507157</v>
+        <v>507097</v>
       </c>
       <c r="R78" t="n">
-        <v>7033090</v>
+        <v>7032620</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9538,7 +9564,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9547,34 +9573,8 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9591,10 +9591,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130107359</v>
+        <v>130107348</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507226</v>
+        <v>507432</v>
       </c>
       <c r="R79" t="n">
-        <v>7032851</v>
+        <v>7032888</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gammal gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9693,10 +9693,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130107346</v>
+        <v>130107359</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9728,10 +9728,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>507521</v>
+        <v>507226</v>
       </c>
       <c r="R80" t="n">
-        <v>7032862</v>
+        <v>7032851</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9795,10 +9795,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130107348</v>
+        <v>130108121</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9806,34 +9806,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>507432</v>
+        <v>506981</v>
       </c>
       <c r="R81" t="n">
-        <v>7032888</v>
+        <v>7032960</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9870,7 +9878,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9881,6 +9889,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9897,37 +9925,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130108130</v>
+        <v>130107313</v>
       </c>
       <c r="B82" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9935,10 +9964,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506954</v>
+        <v>507399</v>
       </c>
       <c r="R82" t="n">
-        <v>7033030</v>
+        <v>7032831</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9983,19 +10012,9 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10013,10 +10032,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130108121</v>
+        <v>130107346</v>
       </c>
       <c r="B83" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,42 +10043,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506981</v>
+        <v>507521</v>
       </c>
       <c r="R83" t="n">
-        <v>7032960</v>
+        <v>7032862</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10096,7 +10107,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10107,26 +10118,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10143,38 +10134,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130107313</v>
+        <v>130108130</v>
       </c>
       <c r="B84" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10182,10 +10172,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>507399</v>
+        <v>506954</v>
       </c>
       <c r="R84" t="n">
-        <v>7032831</v>
+        <v>7033030</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10230,9 +10220,19 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130107349</v>
+        <v>130108114</v>
       </c>
       <c r="B85" t="n">
-        <v>79095</v>
+        <v>83158</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10261,34 +10261,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>507397</v>
+        <v>507064</v>
       </c>
       <c r="R85" t="n">
-        <v>7032912</v>
+        <v>7032974</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10323,19 +10326,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10352,10 +10366,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130107309</v>
+        <v>130107319</v>
       </c>
       <c r="B86" t="n">
-        <v>80229</v>
+        <v>97791</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10363,30 +10377,27 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10394,10 +10405,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>507227</v>
+        <v>507144</v>
       </c>
       <c r="R86" t="n">
-        <v>7032981</v>
+        <v>7033068</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10432,11 +10443,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På en sälg i granskog.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10450,26 +10456,6 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10487,10 +10473,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130108114</v>
+        <v>130107347</v>
       </c>
       <c r="B87" t="n">
-        <v>83073</v>
+        <v>79180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10498,37 +10484,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>507064</v>
+        <v>507473</v>
       </c>
       <c r="R87" t="n">
-        <v>7032974</v>
+        <v>7032872</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10563,30 +10546,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10603,10 +10575,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130107347</v>
+        <v>130108122</v>
       </c>
       <c r="B88" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10614,34 +10586,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>507473</v>
+        <v>506980</v>
       </c>
       <c r="R88" t="n">
-        <v>7032872</v>
+        <v>7032966</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10678,7 +10658,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10689,6 +10669,26 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10705,10 +10705,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130108122</v>
+        <v>130107349</v>
       </c>
       <c r="B89" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10716,42 +10716,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506980</v>
+        <v>507397</v>
       </c>
       <c r="R89" t="n">
-        <v>7032966</v>
+        <v>7032912</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10788,7 +10780,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10799,26 +10791,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10835,10 +10807,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130107319</v>
+        <v>130107309</v>
       </c>
       <c r="B90" t="n">
-        <v>97704</v>
+        <v>80314</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10846,27 +10818,30 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10874,10 +10849,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>507144</v>
+        <v>507227</v>
       </c>
       <c r="R90" t="n">
-        <v>7033068</v>
+        <v>7032981</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10912,6 +10887,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På en sälg i granskog.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -10925,6 +10905,26 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130107322</v>
+        <v>130108117</v>
       </c>
       <c r="B6" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,26 +1161,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507355</v>
+        <v>507057</v>
       </c>
       <c r="R6" t="n">
-        <v>7032906</v>
+        <v>7032982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1233,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,33 +1242,27 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1281,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107354</v>
+        <v>130107360</v>
       </c>
       <c r="B7" t="n">
         <v>79180</v>
@@ -1310,16 +1309,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507440</v>
+        <v>507211</v>
       </c>
       <c r="R7" t="n">
-        <v>7032815</v>
+        <v>7032876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,7 +1358,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,8 +1367,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1383,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130108117</v>
+        <v>130107371</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,42 +1422,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507057</v>
+        <v>507222</v>
       </c>
       <c r="R8" t="n">
-        <v>7032982</v>
+        <v>7033039</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1486,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,26 +1497,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1513,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107360</v>
+        <v>130107341</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1542,19 +1542,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507211</v>
+        <v>507330</v>
       </c>
       <c r="R9" t="n">
-        <v>7032876</v>
+        <v>7032840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1588,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,34 +1597,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1644,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107371</v>
+        <v>130107322</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,34 +1626,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507222</v>
+        <v>507355</v>
       </c>
       <c r="R10" t="n">
-        <v>7033039</v>
+        <v>7032906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,8 +1702,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1746,7 +1746,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107341</v>
+        <v>130107354</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507330</v>
+        <v>507440</v>
       </c>
       <c r="R11" t="n">
-        <v>7032840</v>
+        <v>7032815</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107353</v>
+        <v>130108131</v>
       </c>
       <c r="B15" t="n">
         <v>79180</v>
@@ -2244,16 +2244,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507521</v>
+        <v>506958</v>
       </c>
       <c r="R15" t="n">
-        <v>7032767</v>
+        <v>7032984</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,19 +2291,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2317,7 +2331,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107363</v>
+        <v>130107369</v>
       </c>
       <c r="B16" t="n">
         <v>79180</v>
@@ -2352,10 +2366,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507069</v>
+        <v>507237</v>
       </c>
       <c r="R16" t="n">
-        <v>7033199</v>
+        <v>7033036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107323</v>
+        <v>130107363</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,37 +2444,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507416</v>
+        <v>507069</v>
       </c>
       <c r="R17" t="n">
-        <v>7032925</v>
+        <v>7033199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,7 +2508,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,34 +2517,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2550,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130107369</v>
+        <v>130107323</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,34 +2546,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507237</v>
+        <v>507416</v>
       </c>
       <c r="R18" t="n">
-        <v>7033036</v>
+        <v>7032925</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2625,7 +2613,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,8 +2622,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2652,7 +2666,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108131</v>
+        <v>130107374</v>
       </c>
       <c r="B19" t="n">
         <v>79180</v>
@@ -2681,19 +2695,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506958</v>
+        <v>507101</v>
       </c>
       <c r="R19" t="n">
-        <v>7032984</v>
+        <v>7033240</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,30 +2739,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2768,7 +2768,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107374</v>
+        <v>130107345</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507101</v>
+        <v>507468</v>
       </c>
       <c r="R20" t="n">
-        <v>7033240</v>
+        <v>7032839</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,7 +2870,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107345</v>
+        <v>130107353</v>
       </c>
       <c r="B21" t="n">
         <v>79180</v>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507468</v>
+        <v>507521</v>
       </c>
       <c r="R21" t="n">
-        <v>7032839</v>
+        <v>7032767</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107361</v>
+        <v>130107355</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -3001,19 +3001,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507236</v>
+        <v>507422</v>
       </c>
       <c r="R22" t="n">
-        <v>7032990</v>
+        <v>7032836</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3050,7 +3047,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,34 +3056,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3103,61 +3074,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107328</v>
+        <v>130107356</v>
       </c>
       <c r="B23" t="n">
-        <v>57930</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507190</v>
+        <v>507326</v>
       </c>
       <c r="R23" t="n">
-        <v>7033178</v>
+        <v>7032797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3194,7 +3149,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,11 +3160,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3226,10 +3176,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107355</v>
+        <v>130107307</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,34 +3187,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507422</v>
+        <v>507225</v>
       </c>
       <c r="R24" t="n">
-        <v>7032836</v>
+        <v>7033149</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3301,7 +3263,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,6 +3274,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3328,7 +3315,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107356</v>
+        <v>130107361</v>
       </c>
       <c r="B25" t="n">
         <v>79180</v>
@@ -3357,16 +3344,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507326</v>
+        <v>507236</v>
       </c>
       <c r="R25" t="n">
-        <v>7032797</v>
+        <v>7032990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3393,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,8 +3402,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3430,27 +3446,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107307</v>
+        <v>130107328</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3458,12 +3474,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3477,10 +3497,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507225</v>
+        <v>507190</v>
       </c>
       <c r="R26" t="n">
-        <v>7033149</v>
+        <v>7033178</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,7 +3537,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3532,26 +3552,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107350</v>
+        <v>130107305</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,34 +4172,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507429</v>
+        <v>507427</v>
       </c>
       <c r="R32" t="n">
-        <v>7032901</v>
+        <v>7032906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4236,7 +4244,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4247,6 +4255,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4263,10 +4296,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130107305</v>
+        <v>130108113</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4274,31 +4307,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4306,10 +4334,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507427</v>
+        <v>507086</v>
       </c>
       <c r="R33" t="n">
-        <v>7032906</v>
+        <v>7032654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4344,25 +4372,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4373,14 +4392,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4398,10 +4412,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130108113</v>
+        <v>130107350</v>
       </c>
       <c r="B34" t="n">
-        <v>83158</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,37 +4423,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507086</v>
+        <v>507429</v>
       </c>
       <c r="R34" t="n">
-        <v>7032654</v>
+        <v>7032901</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4474,30 +4485,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B45" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,30 +5646,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5677,10 +5673,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R45" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5715,11 +5711,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5737,22 +5728,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5770,10 +5756,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B46" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5781,26 +5767,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5808,10 +5798,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R46" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5846,6 +5836,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5863,17 +5858,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107365</v>
+        <v>130108128</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5902,34 +5902,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507106</v>
+        <v>507058</v>
       </c>
       <c r="R47" t="n">
-        <v>7033205</v>
+        <v>7032972</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5964,19 +5967,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5993,45 +6007,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107368</v>
+        <v>130107312</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507204</v>
+        <v>507337</v>
       </c>
       <c r="R48" t="n">
-        <v>7033154</v>
+        <v>7032943</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6066,19 +6084,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6095,10 +6114,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130108128</v>
+        <v>130107362</v>
       </c>
       <c r="B49" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6106,37 +6125,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507058</v>
+        <v>507201</v>
       </c>
       <c r="R49" t="n">
-        <v>7032972</v>
+        <v>7032984</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6171,30 +6187,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6211,10 +6216,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107312</v>
+        <v>130107327</v>
       </c>
       <c r="B50" t="n">
-        <v>97791</v>
+        <v>80321</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6222,27 +6227,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6250,7 +6258,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507337</v>
+        <v>507239</v>
       </c>
       <c r="R50" t="n">
         <v>7032943</v>
@@ -6288,6 +6296,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6301,6 +6314,21 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6318,7 +6346,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107362</v>
+        <v>130107365</v>
       </c>
       <c r="B51" t="n">
         <v>79180</v>
@@ -6353,10 +6381,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507201</v>
+        <v>507106</v>
       </c>
       <c r="R51" t="n">
-        <v>7032984</v>
+        <v>7033205</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6393,7 +6421,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6420,52 +6448,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107327</v>
+        <v>130107368</v>
       </c>
       <c r="B52" t="n">
-        <v>80321</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507239</v>
+        <v>507204</v>
       </c>
       <c r="R52" t="n">
-        <v>7032943</v>
+        <v>7033154</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6502,7 +6523,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6511,29 +6532,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130108117</v>
+        <v>130107322</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,31 +1161,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507057</v>
+        <v>507355</v>
       </c>
       <c r="R6" t="n">
-        <v>7032982</v>
+        <v>7032906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1228,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,27 +1237,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1280,7 +1281,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107360</v>
+        <v>130107354</v>
       </c>
       <c r="B7" t="n">
         <v>79180</v>
@@ -1309,19 +1310,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507211</v>
+        <v>507440</v>
       </c>
       <c r="R7" t="n">
-        <v>7032876</v>
+        <v>7032815</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1356,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,34 +1365,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1411,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107371</v>
+        <v>130108117</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,34 +1394,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507222</v>
+        <v>507057</v>
       </c>
       <c r="R8" t="n">
-        <v>7033039</v>
+        <v>7032982</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,7 +1466,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,6 +1477,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1513,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107341</v>
+        <v>130107360</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1542,16 +1542,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507330</v>
+        <v>507211</v>
       </c>
       <c r="R9" t="n">
-        <v>7032840</v>
+        <v>7032876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1591,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,8 +1600,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1615,10 +1644,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107322</v>
+        <v>130107371</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,37 +1655,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507355</v>
+        <v>507222</v>
       </c>
       <c r="R10" t="n">
-        <v>7032906</v>
+        <v>7033039</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1719,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,34 +1728,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1746,7 +1746,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107354</v>
+        <v>130107341</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507440</v>
+        <v>507330</v>
       </c>
       <c r="R11" t="n">
-        <v>7032815</v>
+        <v>7032840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130108131</v>
+        <v>130107353</v>
       </c>
       <c r="B15" t="n">
         <v>79180</v>
@@ -2244,19 +2244,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506958</v>
+        <v>507521</v>
       </c>
       <c r="R15" t="n">
-        <v>7032984</v>
+        <v>7032767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,30 +2288,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2331,7 +2317,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107369</v>
+        <v>130107363</v>
       </c>
       <c r="B16" t="n">
         <v>79180</v>
@@ -2366,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507237</v>
+        <v>507069</v>
       </c>
       <c r="R16" t="n">
-        <v>7033036</v>
+        <v>7033199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107363</v>
+        <v>130107323</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,34 +2430,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507069</v>
+        <v>507416</v>
       </c>
       <c r="R17" t="n">
-        <v>7033199</v>
+        <v>7032925</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,7 +2497,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,8 +2506,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2535,10 +2550,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130107323</v>
+        <v>130107369</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2546,37 +2561,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507416</v>
+        <v>507237</v>
       </c>
       <c r="R18" t="n">
-        <v>7032925</v>
+        <v>7033036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2625,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,34 +2634,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2666,7 +2652,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130107374</v>
+        <v>130108131</v>
       </c>
       <c r="B19" t="n">
         <v>79180</v>
@@ -2695,16 +2681,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507101</v>
+        <v>506958</v>
       </c>
       <c r="R19" t="n">
-        <v>7033240</v>
+        <v>7032984</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,19 +2728,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2768,7 +2768,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107345</v>
+        <v>130107374</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507468</v>
+        <v>507101</v>
       </c>
       <c r="R20" t="n">
-        <v>7032839</v>
+        <v>7033240</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,7 +2870,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107353</v>
+        <v>130107345</v>
       </c>
       <c r="B21" t="n">
         <v>79180</v>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507521</v>
+        <v>507468</v>
       </c>
       <c r="R21" t="n">
-        <v>7032767</v>
+        <v>7032839</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107355</v>
+        <v>130107361</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -3001,16 +3001,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507422</v>
+        <v>507236</v>
       </c>
       <c r="R22" t="n">
-        <v>7032836</v>
+        <v>7032990</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3050,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,8 +3059,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3074,45 +3103,61 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107356</v>
+        <v>130107328</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>57930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507326</v>
+        <v>507190</v>
       </c>
       <c r="R23" t="n">
-        <v>7032797</v>
+        <v>7033178</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,7 +3194,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,6 +3205,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3176,10 +3226,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107307</v>
+        <v>130107355</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,46 +3237,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507225</v>
+        <v>507422</v>
       </c>
       <c r="R24" t="n">
-        <v>7033149</v>
+        <v>7032836</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3263,7 +3301,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,31 +3312,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3315,7 +3328,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107361</v>
+        <v>130107356</v>
       </c>
       <c r="B25" t="n">
         <v>79180</v>
@@ -3344,19 +3357,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507236</v>
+        <v>507326</v>
       </c>
       <c r="R25" t="n">
-        <v>7032990</v>
+        <v>7032797</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3393,7 +3403,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,34 +3412,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3446,27 +3430,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107328</v>
+        <v>130107307</v>
       </c>
       <c r="B26" t="n">
-        <v>57930</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3474,16 +3458,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3497,10 +3477,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507190</v>
+        <v>507225</v>
       </c>
       <c r="R26" t="n">
-        <v>7033178</v>
+        <v>7033149</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3517,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3552,6 +3532,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107332</v>
+        <v>130107339</v>
       </c>
       <c r="B35" t="n">
         <v>79180</v>
@@ -4543,16 +4543,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507011</v>
+        <v>507154</v>
       </c>
       <c r="R35" t="n">
-        <v>7033080</v>
+        <v>7032764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4589,7 +4592,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en stående död granhögstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4598,8 +4601,34 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4616,49 +4645,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107317</v>
+        <v>130107332</v>
       </c>
       <c r="B36" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507267</v>
+        <v>507011</v>
       </c>
       <c r="R36" t="n">
-        <v>7033117</v>
+        <v>7033080</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4693,20 +4718,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4723,37 +4747,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107339</v>
+        <v>130107317</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4761,10 +4786,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507154</v>
+        <v>507267</v>
       </c>
       <c r="R37" t="n">
-        <v>7032764</v>
+        <v>7033117</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4799,11 +4824,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På en stående död granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4817,26 +4837,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,26 +5646,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5673,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R45" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5711,6 +5715,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5728,17 +5737,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5756,10 +5770,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B46" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5767,30 +5781,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5798,10 +5808,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R46" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5836,11 +5846,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5858,22 +5863,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -8810,42 +8810,38 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130108123</v>
+        <v>130107314</v>
       </c>
       <c r="B72" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8853,10 +8849,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506984</v>
+        <v>507176</v>
       </c>
       <c r="R72" t="n">
-        <v>7032983</v>
+        <v>7032962</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8891,38 +8887,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8940,49 +8917,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130107314</v>
+        <v>130107340</v>
       </c>
       <c r="B73" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507176</v>
+        <v>507241</v>
       </c>
       <c r="R73" t="n">
-        <v>7032962</v>
+        <v>7032773</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9017,20 +8990,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9047,7 +9019,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130107340</v>
+        <v>130107351</v>
       </c>
       <c r="B74" t="n">
         <v>79180</v>
@@ -9082,10 +9054,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507241</v>
+        <v>507466</v>
       </c>
       <c r="R74" t="n">
-        <v>7032773</v>
+        <v>7032900</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9122,7 +9094,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9149,45 +9121,49 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130107351</v>
+        <v>130107315</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507466</v>
+        <v>507217</v>
       </c>
       <c r="R75" t="n">
-        <v>7032900</v>
+        <v>7033002</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9222,19 +9198,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9251,38 +9228,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130107315</v>
+        <v>130108123</v>
       </c>
       <c r="B76" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9290,10 +9271,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507217</v>
+        <v>506984</v>
       </c>
       <c r="R76" t="n">
-        <v>7033002</v>
+        <v>7032983</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9328,19 +9309,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9591,7 +9591,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130107348</v>
+        <v>130107359</v>
       </c>
       <c r="B79" t="n">
         <v>79180</v>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507432</v>
+        <v>507226</v>
       </c>
       <c r="R79" t="n">
-        <v>7032888</v>
+        <v>7032851</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9693,10 +9693,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130107359</v>
+        <v>130108121</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9704,34 +9704,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>507226</v>
+        <v>506981</v>
       </c>
       <c r="R80" t="n">
-        <v>7032851</v>
+        <v>7032960</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9768,7 +9776,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9779,6 +9787,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9795,42 +9823,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130108121</v>
+        <v>130107313</v>
       </c>
       <c r="B81" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9838,10 +9862,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506981</v>
+        <v>507399</v>
       </c>
       <c r="R81" t="n">
-        <v>7032960</v>
+        <v>7032831</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9876,38 +9900,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9925,49 +9930,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130107313</v>
+        <v>130107346</v>
       </c>
       <c r="B82" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>507399</v>
+        <v>507521</v>
       </c>
       <c r="R82" t="n">
-        <v>7032831</v>
+        <v>7032862</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10002,20 +10003,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10032,7 +10032,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130107346</v>
+        <v>130108130</v>
       </c>
       <c r="B83" t="n">
         <v>79180</v>
@@ -10061,16 +10061,19 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>507521</v>
+        <v>506954</v>
       </c>
       <c r="R83" t="n">
-        <v>7032862</v>
+        <v>7033030</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10105,19 +10108,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10134,7 +10148,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130108130</v>
+        <v>130107348</v>
       </c>
       <c r="B84" t="n">
         <v>79180</v>
@@ -10163,19 +10177,16 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506954</v>
+        <v>507432</v>
       </c>
       <c r="R84" t="n">
-        <v>7033030</v>
+        <v>7032888</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10210,30 +10221,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -1383,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130108117</v>
+        <v>130107360</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,31 +1394,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507057</v>
+        <v>507211</v>
       </c>
       <c r="R8" t="n">
-        <v>7032982</v>
+        <v>7032876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,12 +1470,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1493,9 +1489,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1513,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107360</v>
+        <v>130107371</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1542,19 +1543,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507211</v>
+        <v>507222</v>
       </c>
       <c r="R9" t="n">
-        <v>7032876</v>
+        <v>7033039</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,34 +1598,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1644,7 +1616,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107371</v>
+        <v>130107341</v>
       </c>
       <c r="B10" t="n">
         <v>79180</v>
@@ -1679,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507222</v>
+        <v>507330</v>
       </c>
       <c r="R10" t="n">
-        <v>7033039</v>
+        <v>7032840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107341</v>
+        <v>130108117</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,34 +1729,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507330</v>
+        <v>507057</v>
       </c>
       <c r="R11" t="n">
-        <v>7032840</v>
+        <v>7032982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,7 +1801,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,6 +1812,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2215,7 +2215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107353</v>
+        <v>130107369</v>
       </c>
       <c r="B15" t="n">
         <v>79180</v>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507521</v>
+        <v>507237</v>
       </c>
       <c r="R15" t="n">
-        <v>7032767</v>
+        <v>7033036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107323</v>
+        <v>130108131</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507416</v>
+        <v>506958</v>
       </c>
       <c r="R17" t="n">
-        <v>7032925</v>
+        <v>7032984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,11 +2495,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2510,29 +2505,19 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2550,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130107369</v>
+        <v>130107323</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,34 +2546,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507237</v>
+        <v>507416</v>
       </c>
       <c r="R18" t="n">
-        <v>7033036</v>
+        <v>7032925</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2625,7 +2613,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,8 +2622,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2652,7 +2666,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108131</v>
+        <v>130107374</v>
       </c>
       <c r="B19" t="n">
         <v>79180</v>
@@ -2681,19 +2695,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506958</v>
+        <v>507101</v>
       </c>
       <c r="R19" t="n">
-        <v>7032984</v>
+        <v>7033240</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,30 +2739,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2768,7 +2768,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107374</v>
+        <v>130107353</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507101</v>
+        <v>507521</v>
       </c>
       <c r="R20" t="n">
-        <v>7033240</v>
+        <v>7032767</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,48 +2972,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107361</v>
+        <v>130107328</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>57930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507236</v>
+        <v>507190</v>
       </c>
       <c r="R22" t="n">
-        <v>7032990</v>
+        <v>7033178</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3050,7 +3063,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,33 +3072,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3103,61 +3095,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107328</v>
+        <v>130107355</v>
       </c>
       <c r="B23" t="n">
-        <v>57930</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507190</v>
+        <v>507422</v>
       </c>
       <c r="R23" t="n">
-        <v>7033178</v>
+        <v>7032836</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3194,7 +3170,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,11 +3181,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3226,7 +3197,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107355</v>
+        <v>130107356</v>
       </c>
       <c r="B24" t="n">
         <v>79180</v>
@@ -3261,10 +3232,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507422</v>
+        <v>507326</v>
       </c>
       <c r="R24" t="n">
-        <v>7032836</v>
+        <v>7032797</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3328,7 +3299,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107356</v>
+        <v>130107361</v>
       </c>
       <c r="B25" t="n">
         <v>79180</v>
@@ -3357,16 +3328,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507326</v>
+        <v>507236</v>
       </c>
       <c r="R25" t="n">
-        <v>7032797</v>
+        <v>7032990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3377,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,8 +3386,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3787,10 +3787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130108126</v>
+        <v>130108127</v>
       </c>
       <c r="B29" t="n">
-        <v>57985</v>
+        <v>80285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,50 +3798,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507059</v>
+        <v>507051</v>
       </c>
       <c r="R29" t="n">
-        <v>7032796</v>
+        <v>7032835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3882,12 +3869,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3905,37 +3908,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130108127</v>
+        <v>130107326</v>
       </c>
       <c r="B30" t="n">
-        <v>80285</v>
+        <v>80321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3943,10 +3950,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507051</v>
+        <v>507353</v>
       </c>
       <c r="R30" t="n">
-        <v>7032835</v>
+        <v>7032907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3981,6 +3988,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4006,9 +4018,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4026,52 +4043,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107326</v>
+        <v>130108126</v>
       </c>
       <c r="B31" t="n">
-        <v>80321</v>
+        <v>57985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507353</v>
+        <v>507059</v>
       </c>
       <c r="R31" t="n">
-        <v>7032907</v>
+        <v>7032796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,44 +4132,18 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130108113</v>
+        <v>130107350</v>
       </c>
       <c r="B33" t="n">
-        <v>83158</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,37 +4307,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507086</v>
+        <v>507429</v>
       </c>
       <c r="R33" t="n">
-        <v>7032654</v>
+        <v>7032901</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4372,30 +4369,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4412,10 +4398,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107350</v>
+        <v>130108113</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>83158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4423,34 +4409,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507429</v>
+        <v>507086</v>
       </c>
       <c r="R34" t="n">
-        <v>7032901</v>
+        <v>7032654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4485,19 +4474,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4747,38 +4747,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107317</v>
+        <v>130107370</v>
       </c>
       <c r="B37" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4786,10 +4785,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507267</v>
+        <v>507211</v>
       </c>
       <c r="R37" t="n">
-        <v>7033117</v>
+        <v>7033009</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4824,6 +4823,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4837,6 +4841,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4854,37 +4878,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107370</v>
+        <v>130107317</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4892,10 +4917,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507211</v>
+        <v>507267</v>
       </c>
       <c r="R38" t="n">
-        <v>7033009</v>
+        <v>7033117</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4930,11 +4955,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4948,26 +4968,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5222,45 +5222,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107342</v>
+        <v>130107311</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507376</v>
+        <v>507355</v>
       </c>
       <c r="R41" t="n">
-        <v>7032813</v>
+        <v>7032851</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5295,19 +5299,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5324,7 +5329,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107364</v>
+        <v>130107342</v>
       </c>
       <c r="B42" t="n">
         <v>79180</v>
@@ -5359,10 +5364,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507091</v>
+        <v>507376</v>
       </c>
       <c r="R42" t="n">
-        <v>7033218</v>
+        <v>7032813</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5399,7 +5404,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5528,49 +5533,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107311</v>
+        <v>130107364</v>
       </c>
       <c r="B44" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507355</v>
+        <v>507091</v>
       </c>
       <c r="R44" t="n">
-        <v>7032851</v>
+        <v>7033218</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,20 +5606,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5891,10 +5891,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130108128</v>
+        <v>130107362</v>
       </c>
       <c r="B47" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5902,37 +5902,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507058</v>
+        <v>507201</v>
       </c>
       <c r="R47" t="n">
-        <v>7032972</v>
+        <v>7032984</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5967,30 +5964,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6007,10 +5993,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107312</v>
+        <v>130107327</v>
       </c>
       <c r="B48" t="n">
-        <v>97791</v>
+        <v>80321</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6018,27 +6004,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6046,7 +6035,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507337</v>
+        <v>507239</v>
       </c>
       <c r="R48" t="n">
         <v>7032943</v>
@@ -6084,6 +6073,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6097,6 +6091,21 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6114,7 +6123,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130107362</v>
+        <v>130107365</v>
       </c>
       <c r="B49" t="n">
         <v>79180</v>
@@ -6149,10 +6158,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507201</v>
+        <v>507106</v>
       </c>
       <c r="R49" t="n">
-        <v>7032984</v>
+        <v>7033205</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6189,7 +6198,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6216,52 +6225,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107327</v>
+        <v>130107368</v>
       </c>
       <c r="B50" t="n">
-        <v>80321</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507239</v>
+        <v>507204</v>
       </c>
       <c r="R50" t="n">
-        <v>7032943</v>
+        <v>7033154</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6298,7 +6300,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6307,29 +6309,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6346,10 +6327,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107365</v>
+        <v>130107310</v>
       </c>
       <c r="B51" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6357,34 +6338,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507106</v>
+        <v>507084</v>
       </c>
       <c r="R51" t="n">
-        <v>7033205</v>
+        <v>7033149</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6421,7 +6406,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6432,6 +6417,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6448,45 +6458,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107368</v>
+        <v>130107312</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507204</v>
+        <v>507337</v>
       </c>
       <c r="R52" t="n">
-        <v>7033154</v>
+        <v>7032943</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6521,19 +6535,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6550,10 +6565,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130107310</v>
+        <v>130108128</v>
       </c>
       <c r="B53" t="n">
-        <v>57823</v>
+        <v>78192</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6561,27 +6576,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6589,10 +6603,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507084</v>
+        <v>507058</v>
       </c>
       <c r="R53" t="n">
-        <v>7033149</v>
+        <v>7032972</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6627,25 +6641,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ53" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6656,14 +6661,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6811,45 +6811,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107358</v>
+        <v>130107318</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507233</v>
+        <v>507226</v>
       </c>
       <c r="R55" t="n">
-        <v>7032821</v>
+        <v>7033130</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6884,19 +6888,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6913,7 +6918,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130107336</v>
+        <v>130107358</v>
       </c>
       <c r="B56" t="n">
         <v>79180</v>
@@ -6948,10 +6953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507081</v>
+        <v>507233</v>
       </c>
       <c r="R56" t="n">
-        <v>7032660</v>
+        <v>7032821</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6988,7 +6993,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7015,10 +7020,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130108124</v>
+        <v>130107336</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7026,42 +7031,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506973</v>
+        <v>507081</v>
       </c>
       <c r="R57" t="n">
-        <v>7032980</v>
+        <v>7032660</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,7 +7095,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7109,26 +7106,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7145,49 +7122,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130107318</v>
+        <v>130107352</v>
       </c>
       <c r="B58" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507226</v>
+        <v>507537</v>
       </c>
       <c r="R58" t="n">
-        <v>7033130</v>
+        <v>7032882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7222,20 +7195,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7252,10 +7224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130107352</v>
+        <v>130108116</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>83158</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7263,34 +7235,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507537</v>
+        <v>506959</v>
       </c>
       <c r="R59" t="n">
-        <v>7032882</v>
+        <v>7032984</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7325,19 +7300,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7354,10 +7340,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130108116</v>
+        <v>130108124</v>
       </c>
       <c r="B60" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7365,26 +7351,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7392,10 +7383,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506959</v>
+        <v>506973</v>
       </c>
       <c r="R60" t="n">
-        <v>7032984</v>
+        <v>7032980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7430,15 +7421,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130108118</v>
+        <v>130107367</v>
       </c>
       <c r="B61" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7481,42 +7481,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506992</v>
+        <v>507157</v>
       </c>
       <c r="R61" t="n">
-        <v>7032926</v>
+        <v>7033174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7553,7 +7545,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7564,26 +7556,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7600,7 +7572,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107367</v>
+        <v>130107335</v>
       </c>
       <c r="B62" t="n">
         <v>79180</v>
@@ -7635,10 +7607,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507157</v>
+        <v>507088</v>
       </c>
       <c r="R62" t="n">
-        <v>7033174</v>
+        <v>7032634</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7675,7 +7647,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7702,10 +7674,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130107303</v>
+        <v>130107325</v>
       </c>
       <c r="B63" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7713,31 +7685,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7745,10 +7712,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507345</v>
+        <v>507225</v>
       </c>
       <c r="R63" t="n">
-        <v>7032953</v>
+        <v>7033115</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7785,7 +7752,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7794,6 +7761,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7804,22 +7772,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7837,10 +7805,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130107330</v>
+        <v>130108118</v>
       </c>
       <c r="B64" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7848,24 +7816,29 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7875,10 +7848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507223</v>
+        <v>506992</v>
       </c>
       <c r="R64" t="n">
-        <v>7032791</v>
+        <v>7032926</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7915,7 +7888,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7924,13 +7897,12 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -7943,14 +7915,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7968,10 +7935,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130107335</v>
+        <v>130107303</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7979,34 +7946,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507088</v>
+        <v>507345</v>
       </c>
       <c r="R65" t="n">
-        <v>7032634</v>
+        <v>7032953</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8043,7 +8018,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8054,6 +8029,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8070,10 +8070,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130107325</v>
+        <v>130107330</v>
       </c>
       <c r="B66" t="n">
-        <v>80285</v>
+        <v>91748</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8081,26 +8081,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507225</v>
+        <v>507223</v>
       </c>
       <c r="R66" t="n">
-        <v>7033115</v>
+        <v>7032791</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8168,22 +8168,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130107302</v>
+        <v>130107337</v>
       </c>
       <c r="B67" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,42 +8212,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507075</v>
+        <v>507084</v>
       </c>
       <c r="R67" t="n">
-        <v>7032759</v>
+        <v>7032690</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8284,7 +8276,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8295,31 +8287,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8336,7 +8303,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130107337</v>
+        <v>130107372</v>
       </c>
       <c r="B68" t="n">
         <v>79180</v>
@@ -8371,10 +8338,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507084</v>
+        <v>507223</v>
       </c>
       <c r="R68" t="n">
-        <v>7032690</v>
+        <v>7033198</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8411,7 +8378,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8438,7 +8405,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130107372</v>
+        <v>130107344</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -8467,16 +8434,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507223</v>
+        <v>507358</v>
       </c>
       <c r="R69" t="n">
-        <v>7033198</v>
+        <v>7032855</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8513,7 +8483,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8522,8 +8492,34 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8540,10 +8536,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130107344</v>
+        <v>130107306</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8551,37 +8547,46 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507358</v>
+        <v>507221</v>
       </c>
       <c r="R70" t="n">
-        <v>7032855</v>
+        <v>7033159</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8618,7 +8623,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8627,7 +8632,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8648,12 +8652,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8671,7 +8675,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130107306</v>
+        <v>130107302</v>
       </c>
       <c r="B71" t="n">
         <v>57826</v>
@@ -8704,24 +8708,20 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507221</v>
+        <v>507075</v>
       </c>
       <c r="R71" t="n">
-        <v>7033159</v>
+        <v>7032759</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8917,45 +8917,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130107340</v>
+        <v>130107315</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507241</v>
+        <v>507217</v>
       </c>
       <c r="R73" t="n">
-        <v>7032773</v>
+        <v>7033002</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8990,19 +8994,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9019,10 +9024,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130107351</v>
+        <v>130108123</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9030,34 +9035,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507466</v>
+        <v>506984</v>
       </c>
       <c r="R74" t="n">
-        <v>7032900</v>
+        <v>7032983</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9094,7 +9107,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9105,6 +9118,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9121,49 +9154,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130107315</v>
+        <v>130107351</v>
       </c>
       <c r="B75" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507217</v>
+        <v>507466</v>
       </c>
       <c r="R75" t="n">
-        <v>7033002</v>
+        <v>7032900</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9198,20 +9227,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt på en gran.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9228,10 +9256,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130108123</v>
+        <v>130107340</v>
       </c>
       <c r="B76" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9239,42 +9267,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506984</v>
+        <v>507241</v>
       </c>
       <c r="R76" t="n">
-        <v>7032983</v>
+        <v>7032773</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9311,7 +9331,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9322,26 +9342,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9591,45 +9591,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130107359</v>
+        <v>130107313</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507226</v>
+        <v>507399</v>
       </c>
       <c r="R79" t="n">
-        <v>7032851</v>
+        <v>7032831</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9664,19 +9668,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9693,10 +9698,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130108121</v>
+        <v>130107359</v>
       </c>
       <c r="B80" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9704,42 +9709,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506981</v>
+        <v>507226</v>
       </c>
       <c r="R80" t="n">
-        <v>7032960</v>
+        <v>7032851</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9776,7 +9773,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9787,26 +9784,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9823,49 +9800,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130107313</v>
+        <v>130107346</v>
       </c>
       <c r="B81" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>507399</v>
+        <v>507521</v>
       </c>
       <c r="R81" t="n">
-        <v>7032831</v>
+        <v>7032862</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9900,20 +9873,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9930,7 +9902,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130107346</v>
+        <v>130107348</v>
       </c>
       <c r="B82" t="n">
         <v>79180</v>
@@ -9965,10 +9937,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>507521</v>
+        <v>507432</v>
       </c>
       <c r="R82" t="n">
-        <v>7032862</v>
+        <v>7032888</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10005,7 +9977,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gammal gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10148,10 +10120,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130107348</v>
+        <v>130108121</v>
       </c>
       <c r="B84" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10159,34 +10131,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>507432</v>
+        <v>506981</v>
       </c>
       <c r="R84" t="n">
-        <v>7032888</v>
+        <v>7032960</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10223,7 +10203,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10234,6 +10214,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10250,37 +10250,38 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130108114</v>
+        <v>130107319</v>
       </c>
       <c r="B85" t="n">
-        <v>83158</v>
+        <v>97791</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10288,10 +10289,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>507064</v>
+        <v>507144</v>
       </c>
       <c r="R85" t="n">
-        <v>7032974</v>
+        <v>7033068</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10336,19 +10337,9 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10366,49 +10357,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130107319</v>
+        <v>130107349</v>
       </c>
       <c r="B86" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>507144</v>
+        <v>507397</v>
       </c>
       <c r="R86" t="n">
-        <v>7033068</v>
+        <v>7032912</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10443,20 +10430,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10473,45 +10459,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130107347</v>
+        <v>130107309</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>507473</v>
+        <v>507227</v>
       </c>
       <c r="R87" t="n">
-        <v>7032872</v>
+        <v>7032981</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10548,7 +10541,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en sälg i granskog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10557,8 +10550,34 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10575,10 +10594,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130108122</v>
+        <v>130108114</v>
       </c>
       <c r="B88" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10586,31 +10605,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10618,10 +10632,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506980</v>
+        <v>507064</v>
       </c>
       <c r="R88" t="n">
-        <v>7032966</v>
+        <v>7032974</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10656,24 +10670,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -10705,7 +10710,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130107349</v>
+        <v>130107347</v>
       </c>
       <c r="B89" t="n">
         <v>79180</v>
@@ -10740,10 +10745,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507397</v>
+        <v>507473</v>
       </c>
       <c r="R89" t="n">
-        <v>7032912</v>
+        <v>7032872</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10807,39 +10812,40 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130107309</v>
+        <v>130108122</v>
       </c>
       <c r="B90" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -10849,10 +10855,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>507227</v>
+        <v>506980</v>
       </c>
       <c r="R90" t="n">
-        <v>7032981</v>
+        <v>7032966</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10889,7 +10895,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På en sälg i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10898,33 +10904,27 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130108125</v>
+        <v>130107338</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506976</v>
+        <v>507073</v>
       </c>
       <c r="R3" t="n">
-        <v>7032983</v>
+        <v>7032765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,31 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -917,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107338</v>
+        <v>130107321</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,34 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507073</v>
+        <v>507522</v>
       </c>
       <c r="R4" t="n">
-        <v>7032765</v>
+        <v>7032834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,8 +971,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107321</v>
+        <v>130108125</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,26 +1026,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507522</v>
+        <v>506976</v>
       </c>
       <c r="R5" t="n">
-        <v>7032834</v>
+        <v>7032983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,33 +1107,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130107322</v>
+        <v>130108117</v>
       </c>
       <c r="B6" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,26 +1161,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507355</v>
+        <v>507057</v>
       </c>
       <c r="R6" t="n">
-        <v>7032906</v>
+        <v>7032982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1233,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,33 +1242,27 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1383,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107360</v>
+        <v>130107371</v>
       </c>
       <c r="B8" t="n">
         <v>79180</v>
@@ -1412,19 +1411,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507211</v>
+        <v>507222</v>
       </c>
       <c r="R8" t="n">
-        <v>7032876</v>
+        <v>7033039</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1457,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,34 +1466,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1514,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107371</v>
+        <v>130107360</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1543,16 +1513,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507222</v>
+        <v>507211</v>
       </c>
       <c r="R9" t="n">
-        <v>7033039</v>
+        <v>7032876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1562,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,8 +1571,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1718,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130108117</v>
+        <v>130107322</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,31 +1728,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1761,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507057</v>
+        <v>507355</v>
       </c>
       <c r="R11" t="n">
-        <v>7032982</v>
+        <v>7032906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,27 +1804,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107369</v>
+        <v>130107363</v>
       </c>
       <c r="B15" t="n">
         <v>79180</v>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507237</v>
+        <v>507069</v>
       </c>
       <c r="R15" t="n">
-        <v>7033036</v>
+        <v>7033199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107363</v>
+        <v>130107353</v>
       </c>
       <c r="B16" t="n">
         <v>79180</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507069</v>
+        <v>507521</v>
       </c>
       <c r="R16" t="n">
-        <v>7033199</v>
+        <v>7032767</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130107323</v>
+        <v>130107369</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2546,37 +2546,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507416</v>
+        <v>507237</v>
       </c>
       <c r="R18" t="n">
-        <v>7032925</v>
+        <v>7033036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2610,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,34 +2619,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2768,7 +2739,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107353</v>
+        <v>130107345</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2803,10 +2774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507521</v>
+        <v>507468</v>
       </c>
       <c r="R20" t="n">
-        <v>7032767</v>
+        <v>7032839</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2870,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107345</v>
+        <v>130107323</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,34 +2852,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507468</v>
+        <v>507416</v>
       </c>
       <c r="R21" t="n">
-        <v>7032839</v>
+        <v>7032925</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2919,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2954,8 +2928,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2972,61 +2972,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107328</v>
+        <v>130107356</v>
       </c>
       <c r="B22" t="n">
-        <v>57930</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507190</v>
+        <v>507326</v>
       </c>
       <c r="R22" t="n">
-        <v>7033178</v>
+        <v>7032797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3063,7 +3047,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,11 +3058,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3197,7 +3176,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107356</v>
+        <v>130107361</v>
       </c>
       <c r="B24" t="n">
         <v>79180</v>
@@ -3226,16 +3205,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507326</v>
+        <v>507236</v>
       </c>
       <c r="R24" t="n">
-        <v>7032797</v>
+        <v>7032990</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3272,7 +3254,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,8 +3263,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3299,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107361</v>
+        <v>130107307</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,37 +3318,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507236</v>
+        <v>507225</v>
       </c>
       <c r="R25" t="n">
-        <v>7032990</v>
+        <v>7033149</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3377,7 +3394,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,7 +3403,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3407,12 +3423,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3430,27 +3446,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107307</v>
+        <v>130107328</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3458,12 +3474,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3477,10 +3497,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507225</v>
+        <v>507190</v>
       </c>
       <c r="R26" t="n">
-        <v>7033149</v>
+        <v>7033178</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,7 +3537,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3532,26 +3552,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,34 +3580,50 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R27" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,11 +3658,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3655,6 +3666,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3671,37 +3687,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130108115</v>
+        <v>130107326</v>
       </c>
       <c r="B28" t="n">
-        <v>83158</v>
+        <v>80321</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3709,10 +3729,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506966</v>
+        <v>507353</v>
       </c>
       <c r="R28" t="n">
-        <v>7032974</v>
+        <v>7032907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3747,6 +3767,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3757,19 +3782,29 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3787,10 +3822,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130108127</v>
+        <v>130107366</v>
       </c>
       <c r="B29" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,37 +3833,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507051</v>
+        <v>507149</v>
       </c>
       <c r="R29" t="n">
-        <v>7032835</v>
+        <v>7033155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3863,35 +3895,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3908,41 +3924,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107326</v>
+        <v>130108127</v>
       </c>
       <c r="B30" t="n">
-        <v>80321</v>
+        <v>80285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3950,10 +3962,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507353</v>
+        <v>507051</v>
       </c>
       <c r="R30" t="n">
-        <v>7032907</v>
+        <v>7032835</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3988,11 +4000,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4018,14 +4025,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4043,10 +4045,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130108126</v>
+        <v>130108115</v>
       </c>
       <c r="B31" t="n">
-        <v>57985</v>
+        <v>83158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4054,50 +4056,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507059</v>
+        <v>506966</v>
       </c>
       <c r="R31" t="n">
-        <v>7032796</v>
+        <v>7032974</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4138,12 +4127,23 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107305</v>
+        <v>130107350</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,42 +4172,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507427</v>
+        <v>507429</v>
       </c>
       <c r="R32" t="n">
-        <v>7032906</v>
+        <v>7032901</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4244,7 +4236,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,31 +4247,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4296,10 +4263,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130107350</v>
+        <v>130108113</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>83158</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,34 +4274,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507429</v>
+        <v>507086</v>
       </c>
       <c r="R33" t="n">
-        <v>7032901</v>
+        <v>7032654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4369,19 +4339,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4398,10 +4379,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130108113</v>
+        <v>130107305</v>
       </c>
       <c r="B34" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,26 +4390,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4436,10 +4422,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507086</v>
+        <v>507427</v>
       </c>
       <c r="R34" t="n">
-        <v>7032654</v>
+        <v>7032906</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4474,16 +4460,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4494,9 +4489,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107339</v>
+        <v>130107332</v>
       </c>
       <c r="B35" t="n">
         <v>79180</v>
@@ -4543,19 +4543,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507154</v>
+        <v>507011</v>
       </c>
       <c r="R35" t="n">
-        <v>7032764</v>
+        <v>7033080</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4592,7 +4589,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På en stående död granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4601,34 +4598,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4645,7 +4616,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107332</v>
+        <v>130107370</v>
       </c>
       <c r="B36" t="n">
         <v>79180</v>
@@ -4674,16 +4645,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507011</v>
+        <v>507211</v>
       </c>
       <c r="R36" t="n">
-        <v>7033080</v>
+        <v>7033009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4720,7 +4694,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4729,8 +4703,34 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4747,7 +4747,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107370</v>
+        <v>130107339</v>
       </c>
       <c r="B37" t="n">
         <v>79180</v>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507211</v>
+        <v>507154</v>
       </c>
       <c r="R37" t="n">
-        <v>7033009</v>
+        <v>7032764</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På en stående död granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107343</v>
+        <v>130107329</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>91724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,34 +4996,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507356</v>
+        <v>507152</v>
       </c>
       <c r="R39" t="n">
-        <v>7032842</v>
+        <v>7033148</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5060,7 +5067,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,8 +5076,34 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5087,10 +5120,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130107329</v>
+        <v>130107343</v>
       </c>
       <c r="B40" t="n">
-        <v>91724</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5098,41 +5131,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507152</v>
+        <v>507356</v>
       </c>
       <c r="R40" t="n">
-        <v>7033148</v>
+        <v>7032842</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5169,7 +5195,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5178,34 +5204,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5222,49 +5222,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107311</v>
+        <v>130107357</v>
       </c>
       <c r="B41" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507355</v>
+        <v>507283</v>
       </c>
       <c r="R41" t="n">
-        <v>7032851</v>
+        <v>7032795</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5299,20 +5295,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5431,7 +5426,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130107357</v>
+        <v>130107364</v>
       </c>
       <c r="B43" t="n">
         <v>79180</v>
@@ -5466,10 +5461,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507283</v>
+        <v>507091</v>
       </c>
       <c r="R43" t="n">
-        <v>7032795</v>
+        <v>7033218</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5506,7 +5501,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5533,45 +5528,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107364</v>
+        <v>130107311</v>
       </c>
       <c r="B44" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507091</v>
+        <v>507355</v>
       </c>
       <c r="R44" t="n">
-        <v>7033218</v>
+        <v>7032851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5606,19 +5605,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B45" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,30 +5646,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5677,10 +5673,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R45" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5715,11 +5711,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5737,22 +5728,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5770,10 +5756,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B46" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5781,26 +5767,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5808,10 +5798,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R46" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5846,6 +5836,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5863,17 +5858,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5891,45 +5891,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107362</v>
+        <v>130107312</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507201</v>
+        <v>507337</v>
       </c>
       <c r="R47" t="n">
-        <v>7032984</v>
+        <v>7032943</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5964,19 +5968,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5993,41 +5998,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107327</v>
+        <v>130108128</v>
       </c>
       <c r="B48" t="n">
-        <v>80321</v>
+        <v>78192</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6035,10 +6036,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507239</v>
+        <v>507058</v>
       </c>
       <c r="R48" t="n">
-        <v>7032943</v>
+        <v>7032972</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6073,11 +6074,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6088,24 +6084,19 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6123,7 +6114,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130107365</v>
+        <v>130107362</v>
       </c>
       <c r="B49" t="n">
         <v>79180</v>
@@ -6158,10 +6149,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507106</v>
+        <v>507201</v>
       </c>
       <c r="R49" t="n">
-        <v>7033205</v>
+        <v>7032984</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6198,7 +6189,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6225,10 +6216,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107368</v>
+        <v>130107310</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6236,34 +6227,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507204</v>
+        <v>507084</v>
       </c>
       <c r="R50" t="n">
-        <v>7033154</v>
+        <v>7033149</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6300,7 +6295,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6311,6 +6306,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6327,10 +6347,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107310</v>
+        <v>130107365</v>
       </c>
       <c r="B51" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6338,38 +6358,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507084</v>
+        <v>507106</v>
       </c>
       <c r="R51" t="n">
-        <v>7033149</v>
+        <v>7033205</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6406,7 +6422,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6417,31 +6433,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6458,49 +6449,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107312</v>
+        <v>130107368</v>
       </c>
       <c r="B52" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507337</v>
+        <v>507204</v>
       </c>
       <c r="R52" t="n">
-        <v>7032943</v>
+        <v>7033154</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6535,20 +6522,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6565,37 +6551,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130108128</v>
+        <v>130107327</v>
       </c>
       <c r="B53" t="n">
-        <v>78192</v>
+        <v>80321</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6603,10 +6593,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507058</v>
+        <v>507239</v>
       </c>
       <c r="R53" t="n">
-        <v>7032972</v>
+        <v>7032943</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6641,6 +6631,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6651,19 +6646,24 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6811,49 +6811,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107318</v>
+        <v>130107352</v>
       </c>
       <c r="B55" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507226</v>
+        <v>507537</v>
       </c>
       <c r="R55" t="n">
-        <v>7033130</v>
+        <v>7032882</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6888,20 +6884,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7122,10 +7117,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130107352</v>
+        <v>130108116</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>83158</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7133,34 +7128,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507537</v>
+        <v>506959</v>
       </c>
       <c r="R58" t="n">
-        <v>7032882</v>
+        <v>7032984</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7195,19 +7193,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7224,10 +7233,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130108116</v>
+        <v>130108124</v>
       </c>
       <c r="B59" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7235,26 +7244,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7262,10 +7276,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506959</v>
+        <v>506973</v>
       </c>
       <c r="R59" t="n">
-        <v>7032984</v>
+        <v>7032980</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7300,15 +7314,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -7340,42 +7363,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130108124</v>
+        <v>130107318</v>
       </c>
       <c r="B60" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7383,10 +7402,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506973</v>
+        <v>507226</v>
       </c>
       <c r="R60" t="n">
-        <v>7032980</v>
+        <v>7033130</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7421,38 +7440,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7470,10 +7470,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130107367</v>
+        <v>130107330</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7481,34 +7481,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507157</v>
+        <v>507223</v>
       </c>
       <c r="R61" t="n">
-        <v>7033174</v>
+        <v>7032791</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,7 +7548,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7554,8 +7557,34 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7572,7 +7601,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107335</v>
+        <v>130107367</v>
       </c>
       <c r="B62" t="n">
         <v>79180</v>
@@ -7607,10 +7636,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507088</v>
+        <v>507157</v>
       </c>
       <c r="R62" t="n">
-        <v>7032634</v>
+        <v>7033174</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7647,7 +7676,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7674,10 +7703,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130107325</v>
+        <v>130107335</v>
       </c>
       <c r="B63" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7685,37 +7714,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507225</v>
+        <v>507088</v>
       </c>
       <c r="R63" t="n">
-        <v>7033115</v>
+        <v>7032634</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7752,7 +7778,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7761,34 +7787,8 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7805,10 +7805,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130108118</v>
+        <v>130107325</v>
       </c>
       <c r="B64" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7816,31 +7816,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7848,10 +7843,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506992</v>
+        <v>507225</v>
       </c>
       <c r="R64" t="n">
-        <v>7032926</v>
+        <v>7033115</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7888,7 +7883,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7897,27 +7892,33 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7935,7 +7936,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130107303</v>
+        <v>130108118</v>
       </c>
       <c r="B65" t="n">
         <v>57826</v>
@@ -7968,7 +7969,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7978,10 +7979,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507345</v>
+        <v>506992</v>
       </c>
       <c r="R65" t="n">
-        <v>7032953</v>
+        <v>7032926</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8018,7 +8019,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8032,7 +8033,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -8045,14 +8046,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8070,10 +8066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130107330</v>
+        <v>130107303</v>
       </c>
       <c r="B66" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8081,24 +8077,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8108,10 +8109,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507223</v>
+        <v>507345</v>
       </c>
       <c r="R66" t="n">
-        <v>7032791</v>
+        <v>7032953</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8148,7 +8149,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8157,7 +8158,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130107337</v>
+        <v>130107306</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,34 +8212,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507084</v>
+        <v>507221</v>
       </c>
       <c r="R67" t="n">
-        <v>7032690</v>
+        <v>7033159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8276,7 +8288,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8287,6 +8299,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8303,10 +8340,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130107372</v>
+        <v>130107302</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8314,34 +8351,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507223</v>
+        <v>507075</v>
       </c>
       <c r="R68" t="n">
-        <v>7033198</v>
+        <v>7032759</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8378,7 +8423,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8389,6 +8434,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8405,7 +8475,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130107344</v>
+        <v>130107372</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -8434,19 +8504,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507358</v>
+        <v>507223</v>
       </c>
       <c r="R69" t="n">
-        <v>7032855</v>
+        <v>7033198</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8483,7 +8550,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8492,34 +8559,8 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8536,10 +8577,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130107306</v>
+        <v>130107344</v>
       </c>
       <c r="B70" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8547,46 +8588,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507221</v>
+        <v>507358</v>
       </c>
       <c r="R70" t="n">
-        <v>7033159</v>
+        <v>7032855</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8623,7 +8655,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8632,6 +8664,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8652,12 +8685,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8675,10 +8708,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130107302</v>
+        <v>130107337</v>
       </c>
       <c r="B71" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8686,42 +8719,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507075</v>
+        <v>507084</v>
       </c>
       <c r="R71" t="n">
-        <v>7032759</v>
+        <v>7032690</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8758,7 +8783,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8769,31 +8794,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8810,49 +8810,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130107314</v>
+        <v>130107340</v>
       </c>
       <c r="B72" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507176</v>
+        <v>507241</v>
       </c>
       <c r="R72" t="n">
-        <v>7032962</v>
+        <v>7032773</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8887,20 +8883,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8917,49 +8912,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130107315</v>
+        <v>130107351</v>
       </c>
       <c r="B73" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507217</v>
+        <v>507466</v>
       </c>
       <c r="R73" t="n">
-        <v>7033002</v>
+        <v>7032900</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8994,20 +8985,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt på en gran.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9154,45 +9144,49 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130107351</v>
+        <v>130107315</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507466</v>
+        <v>507217</v>
       </c>
       <c r="R75" t="n">
-        <v>7032900</v>
+        <v>7033002</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9227,19 +9221,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9256,45 +9251,49 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130107340</v>
+        <v>130107314</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507241</v>
+        <v>507176</v>
       </c>
       <c r="R76" t="n">
-        <v>7032773</v>
+        <v>7032962</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9329,19 +9328,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9591,38 +9591,42 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130107313</v>
+        <v>130108121</v>
       </c>
       <c r="B79" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9630,10 +9634,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507399</v>
+        <v>506981</v>
       </c>
       <c r="R79" t="n">
-        <v>7032831</v>
+        <v>7032960</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9668,19 +9672,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9698,7 +9721,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130107359</v>
+        <v>130107348</v>
       </c>
       <c r="B80" t="n">
         <v>79180</v>
@@ -9733,10 +9756,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>507226</v>
+        <v>507432</v>
       </c>
       <c r="R80" t="n">
-        <v>7032851</v>
+        <v>7032888</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9773,7 +9796,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gammal gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9902,7 +9925,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130107348</v>
+        <v>130108130</v>
       </c>
       <c r="B82" t="n">
         <v>79180</v>
@@ -9931,16 +9954,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>507432</v>
+        <v>506954</v>
       </c>
       <c r="R82" t="n">
-        <v>7032888</v>
+        <v>7033030</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9975,19 +10001,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10004,7 +10041,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130108130</v>
+        <v>130107359</v>
       </c>
       <c r="B83" t="n">
         <v>79180</v>
@@ -10033,19 +10070,16 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506954</v>
+        <v>507226</v>
       </c>
       <c r="R83" t="n">
-        <v>7033030</v>
+        <v>7032851</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10080,30 +10114,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10120,42 +10143,38 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130108121</v>
+        <v>130107313</v>
       </c>
       <c r="B84" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10163,10 +10182,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506981</v>
+        <v>507399</v>
       </c>
       <c r="R84" t="n">
-        <v>7032960</v>
+        <v>7032831</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10201,38 +10220,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10250,49 +10250,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130107319</v>
+        <v>130107347</v>
       </c>
       <c r="B85" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>507144</v>
+        <v>507473</v>
       </c>
       <c r="R85" t="n">
-        <v>7033068</v>
+        <v>7032872</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10327,20 +10323,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10710,10 +10705,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130107347</v>
+        <v>130108122</v>
       </c>
       <c r="B89" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10721,34 +10716,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507473</v>
+        <v>506980</v>
       </c>
       <c r="R89" t="n">
-        <v>7032872</v>
+        <v>7032966</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10785,7 +10788,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10796,6 +10799,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10812,42 +10835,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130108122</v>
+        <v>130107319</v>
       </c>
       <c r="B90" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10855,10 +10874,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>506980</v>
+        <v>507144</v>
       </c>
       <c r="R90" t="n">
-        <v>7032966</v>
+        <v>7033068</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10893,38 +10912,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107316</v>
+        <v>130107321</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>80285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507075</v>
+        <v>507522</v>
       </c>
       <c r="R2" t="n">
-        <v>7033179</v>
+        <v>7032834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,6 +751,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,7 +768,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107338</v>
+        <v>130108125</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +817,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507073</v>
+        <v>506976</v>
       </c>
       <c r="R3" t="n">
-        <v>7032765</v>
+        <v>7032983</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,6 +900,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107321</v>
+        <v>130107338</v>
       </c>
       <c r="B4" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +952,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507522</v>
+        <v>507073</v>
       </c>
       <c r="R4" t="n">
-        <v>7032834</v>
+        <v>7032765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,7 +1016,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,34 +1025,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1015,42 +1043,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130108125</v>
+        <v>130107316</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506976</v>
+        <v>507075</v>
       </c>
       <c r="R5" t="n">
-        <v>7032983</v>
+        <v>7033179</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,43 +1120,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130108117</v>
+        <v>130107322</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,31 +1161,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507057</v>
+        <v>507355</v>
       </c>
       <c r="R6" t="n">
-        <v>7032982</v>
+        <v>7032906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1228,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,27 +1237,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1382,7 +1383,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107371</v>
+        <v>130107360</v>
       </c>
       <c r="B8" t="n">
         <v>79180</v>
@@ -1411,16 +1412,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507222</v>
+        <v>507211</v>
       </c>
       <c r="R8" t="n">
-        <v>7033039</v>
+        <v>7032876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,8 +1470,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1484,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107360</v>
+        <v>130107371</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1513,19 +1543,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507211</v>
+        <v>507222</v>
       </c>
       <c r="R9" t="n">
-        <v>7032876</v>
+        <v>7033039</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,34 +1598,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1717,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107322</v>
+        <v>130108117</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,26 +1729,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1755,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507355</v>
+        <v>507057</v>
       </c>
       <c r="R11" t="n">
-        <v>7032906</v>
+        <v>7032982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1801,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,33 +1810,27 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130107373</v>
+        <v>130107304</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,34 +1859,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507202</v>
+        <v>507441</v>
       </c>
       <c r="R12" t="n">
-        <v>7033195</v>
+        <v>7032908</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,7 +1931,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,6 +1942,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1950,7 +1983,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107304</v>
+        <v>130108119</v>
       </c>
       <c r="B13" t="n">
         <v>57826</v>
@@ -1993,10 +2026,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507441</v>
+        <v>506988</v>
       </c>
       <c r="R13" t="n">
-        <v>7032908</v>
+        <v>7032934</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2066,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,7 +2080,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2060,14 +2093,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2085,10 +2113,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130108119</v>
+        <v>130107373</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,42 +2124,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506988</v>
+        <v>507202</v>
       </c>
       <c r="R14" t="n">
-        <v>7032934</v>
+        <v>7033195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2188,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,26 +2199,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2215,10 +2215,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107363</v>
+        <v>130107323</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,34 +2226,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507069</v>
+        <v>507416</v>
       </c>
       <c r="R15" t="n">
-        <v>7033199</v>
+        <v>7032925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2290,7 +2293,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,8 +2302,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2317,7 +2346,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107353</v>
+        <v>130107369</v>
       </c>
       <c r="B16" t="n">
         <v>79180</v>
@@ -2352,10 +2381,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507521</v>
+        <v>507237</v>
       </c>
       <c r="R16" t="n">
-        <v>7032767</v>
+        <v>7033036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,7 +2448,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130108131</v>
+        <v>130107363</v>
       </c>
       <c r="B17" t="n">
         <v>79180</v>
@@ -2448,19 +2477,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506958</v>
+        <v>507069</v>
       </c>
       <c r="R17" t="n">
-        <v>7032984</v>
+        <v>7033199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,30 +2521,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2535,7 +2550,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130107369</v>
+        <v>130108131</v>
       </c>
       <c r="B18" t="n">
         <v>79180</v>
@@ -2564,16 +2579,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507237</v>
+        <v>506958</v>
       </c>
       <c r="R18" t="n">
-        <v>7033036</v>
+        <v>7032984</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,19 +2626,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2739,7 +2768,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107345</v>
+        <v>130107353</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2774,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507468</v>
+        <v>507521</v>
       </c>
       <c r="R20" t="n">
-        <v>7032839</v>
+        <v>7032767</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,10 +2870,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107323</v>
+        <v>130107345</v>
       </c>
       <c r="B21" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2852,37 +2881,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507416</v>
+        <v>507468</v>
       </c>
       <c r="R21" t="n">
-        <v>7032925</v>
+        <v>7032839</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2945,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,34 +2954,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2972,7 +2972,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107356</v>
+        <v>130107355</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507326</v>
+        <v>507422</v>
       </c>
       <c r="R22" t="n">
-        <v>7032797</v>
+        <v>7032836</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107355</v>
+        <v>130107356</v>
       </c>
       <c r="B23" t="n">
         <v>79180</v>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507422</v>
+        <v>507326</v>
       </c>
       <c r="R23" t="n">
-        <v>7032836</v>
+        <v>7032797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130108126</v>
+        <v>130107366</v>
       </c>
       <c r="B27" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,50 +3580,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507059</v>
+        <v>507149</v>
       </c>
       <c r="R27" t="n">
-        <v>7032796</v>
+        <v>7033155</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3658,6 +3642,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3666,11 +3655,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3687,41 +3671,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107326</v>
+        <v>130108115</v>
       </c>
       <c r="B28" t="n">
-        <v>80321</v>
+        <v>83158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3729,10 +3709,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507353</v>
+        <v>506966</v>
       </c>
       <c r="R28" t="n">
-        <v>7032907</v>
+        <v>7032974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3767,11 +3747,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3782,29 +3757,19 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3822,10 +3787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3833,34 +3798,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R29" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3895,11 +3876,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3908,6 +3884,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4045,37 +4026,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130108115</v>
+        <v>130107326</v>
       </c>
       <c r="B31" t="n">
-        <v>83158</v>
+        <v>80321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4083,10 +4068,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506966</v>
+        <v>507353</v>
       </c>
       <c r="R31" t="n">
-        <v>7032974</v>
+        <v>7032907</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4121,6 +4106,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4131,19 +4121,29 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107350</v>
+        <v>130107305</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,34 +4172,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507429</v>
+        <v>507427</v>
       </c>
       <c r="R32" t="n">
-        <v>7032901</v>
+        <v>7032906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4236,7 +4244,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4247,6 +4255,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4263,10 +4296,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130108113</v>
+        <v>130107350</v>
       </c>
       <c r="B33" t="n">
-        <v>83158</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4274,37 +4307,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507086</v>
+        <v>507429</v>
       </c>
       <c r="R33" t="n">
-        <v>7032654</v>
+        <v>7032901</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4339,30 +4369,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4379,10 +4398,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107305</v>
+        <v>130108113</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4390,31 +4409,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4422,10 +4436,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507427</v>
+        <v>507086</v>
       </c>
       <c r="R34" t="n">
-        <v>7032906</v>
+        <v>7032654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4460,25 +4474,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4489,14 +4494,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107332</v>
+        <v>130107339</v>
       </c>
       <c r="B35" t="n">
         <v>79180</v>
@@ -4543,16 +4543,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507011</v>
+        <v>507154</v>
       </c>
       <c r="R35" t="n">
-        <v>7033080</v>
+        <v>7032764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4589,7 +4592,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en stående död granhögstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4598,8 +4601,34 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4616,7 +4645,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107370</v>
+        <v>130107332</v>
       </c>
       <c r="B36" t="n">
         <v>79180</v>
@@ -4645,19 +4674,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507211</v>
+        <v>507011</v>
       </c>
       <c r="R36" t="n">
-        <v>7033009</v>
+        <v>7033080</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4694,7 +4720,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4703,34 +4729,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4747,7 +4747,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107339</v>
+        <v>130107370</v>
       </c>
       <c r="B37" t="n">
         <v>79180</v>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507154</v>
+        <v>507211</v>
       </c>
       <c r="R37" t="n">
-        <v>7032764</v>
+        <v>7033009</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På en stående död granhögstubbe.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107357</v>
+        <v>130107342</v>
       </c>
       <c r="B41" t="n">
         <v>79180</v>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507283</v>
+        <v>507376</v>
       </c>
       <c r="R41" t="n">
-        <v>7032795</v>
+        <v>7032813</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107342</v>
+        <v>130107357</v>
       </c>
       <c r="B42" t="n">
         <v>79180</v>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507376</v>
+        <v>507283</v>
       </c>
       <c r="R42" t="n">
-        <v>7032813</v>
+        <v>7032795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,26 +5646,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5673,10 +5677,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R45" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5711,6 +5715,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5728,17 +5737,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5756,10 +5770,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B46" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5767,30 +5781,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5798,10 +5808,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R46" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5836,11 +5846,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5858,22 +5863,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107312</v>
+        <v>130107327</v>
       </c>
       <c r="B47" t="n">
-        <v>97791</v>
+        <v>80321</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5902,27 +5902,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5930,7 +5933,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507337</v>
+        <v>507239</v>
       </c>
       <c r="R47" t="n">
         <v>7032943</v>
@@ -5968,6 +5971,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5981,6 +5989,21 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5998,10 +6021,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130108128</v>
+        <v>130107310</v>
       </c>
       <c r="B48" t="n">
-        <v>78192</v>
+        <v>57823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6009,26 +6032,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6036,10 +6060,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507058</v>
+        <v>507084</v>
       </c>
       <c r="R48" t="n">
-        <v>7032972</v>
+        <v>7033149</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6074,16 +6098,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6094,9 +6127,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6216,10 +6254,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107310</v>
+        <v>130107365</v>
       </c>
       <c r="B50" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6227,38 +6265,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507084</v>
+        <v>507106</v>
       </c>
       <c r="R50" t="n">
-        <v>7033149</v>
+        <v>7033205</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6295,7 +6329,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6306,31 +6340,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6347,7 +6356,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107365</v>
+        <v>130107368</v>
       </c>
       <c r="B51" t="n">
         <v>79180</v>
@@ -6382,10 +6391,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507106</v>
+        <v>507204</v>
       </c>
       <c r="R51" t="n">
-        <v>7033205</v>
+        <v>7033154</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6422,7 +6431,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6449,10 +6458,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107368</v>
+        <v>130108128</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6460,34 +6469,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507204</v>
+        <v>507058</v>
       </c>
       <c r="R52" t="n">
-        <v>7033154</v>
+        <v>7032972</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6522,19 +6534,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6551,10 +6574,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130107327</v>
+        <v>130107312</v>
       </c>
       <c r="B53" t="n">
-        <v>80321</v>
+        <v>97791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6562,30 +6585,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6593,7 +6613,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507239</v>
+        <v>507337</v>
       </c>
       <c r="R53" t="n">
         <v>7032943</v>
@@ -6631,11 +6651,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6649,21 +6664,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107352</v>
+        <v>130108124</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6822,34 +6822,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507537</v>
+        <v>506973</v>
       </c>
       <c r="R55" t="n">
-        <v>7032882</v>
+        <v>7032980</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6886,7 +6894,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6897,6 +6905,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7117,10 +7145,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130108116</v>
+        <v>130107352</v>
       </c>
       <c r="B58" t="n">
-        <v>83158</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,37 +7156,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506959</v>
+        <v>507537</v>
       </c>
       <c r="R58" t="n">
-        <v>7032984</v>
+        <v>7032882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7193,30 +7218,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7233,10 +7247,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130108124</v>
+        <v>130108116</v>
       </c>
       <c r="B59" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7244,31 +7258,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7276,10 +7285,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506973</v>
+        <v>506959</v>
       </c>
       <c r="R59" t="n">
-        <v>7032980</v>
+        <v>7032984</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7314,24 +7323,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130107330</v>
+        <v>130107367</v>
       </c>
       <c r="B61" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7481,37 +7481,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507223</v>
+        <v>507157</v>
       </c>
       <c r="R61" t="n">
-        <v>7032791</v>
+        <v>7033174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7548,7 +7545,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7557,34 +7554,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7601,10 +7572,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107367</v>
+        <v>130107330</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7612,34 +7583,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507157</v>
+        <v>507223</v>
       </c>
       <c r="R62" t="n">
-        <v>7033174</v>
+        <v>7032791</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7676,7 +7650,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7685,8 +7659,34 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8475,7 +8475,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130107372</v>
+        <v>130107337</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507223</v>
+        <v>507084</v>
       </c>
       <c r="R69" t="n">
-        <v>7033198</v>
+        <v>7032690</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8577,7 +8577,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130107344</v>
+        <v>130107372</v>
       </c>
       <c r="B70" t="n">
         <v>79180</v>
@@ -8606,19 +8606,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507358</v>
+        <v>507223</v>
       </c>
       <c r="R70" t="n">
-        <v>7032855</v>
+        <v>7033198</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8655,7 +8652,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8664,34 +8661,8 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8708,7 +8679,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130107337</v>
+        <v>130107344</v>
       </c>
       <c r="B71" t="n">
         <v>79180</v>
@@ -8737,16 +8708,19 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507084</v>
+        <v>507358</v>
       </c>
       <c r="R71" t="n">
-        <v>7032690</v>
+        <v>7032855</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8783,7 +8757,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8792,8 +8766,34 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130107340</v>
+        <v>130108123</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8821,34 +8821,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507241</v>
+        <v>506984</v>
       </c>
       <c r="R72" t="n">
-        <v>7032773</v>
+        <v>7032983</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8885,7 +8893,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8896,6 +8904,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9014,10 +9042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130108123</v>
+        <v>130107340</v>
       </c>
       <c r="B74" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9025,42 +9053,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506984</v>
+        <v>507241</v>
       </c>
       <c r="R74" t="n">
-        <v>7032983</v>
+        <v>7032773</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9097,7 +9117,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9108,26 +9128,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9144,7 +9144,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130107315</v>
+        <v>130107314</v>
       </c>
       <c r="B75" t="n">
         <v>97791</v>
@@ -9183,10 +9183,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507217</v>
+        <v>507176</v>
       </c>
       <c r="R75" t="n">
-        <v>7033002</v>
+        <v>7032962</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9251,7 +9251,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130107314</v>
+        <v>130107315</v>
       </c>
       <c r="B76" t="n">
         <v>97791</v>
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507176</v>
+        <v>507217</v>
       </c>
       <c r="R76" t="n">
-        <v>7032962</v>
+        <v>7033002</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9721,7 +9721,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130107348</v>
+        <v>130107359</v>
       </c>
       <c r="B80" t="n">
         <v>79180</v>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>507432</v>
+        <v>507226</v>
       </c>
       <c r="R80" t="n">
-        <v>7032888</v>
+        <v>7032851</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9925,7 +9925,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130108130</v>
+        <v>130107348</v>
       </c>
       <c r="B82" t="n">
         <v>79180</v>
@@ -9954,19 +9954,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506954</v>
+        <v>507432</v>
       </c>
       <c r="R82" t="n">
-        <v>7033030</v>
+        <v>7032888</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10001,30 +9998,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10041,7 +10027,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130107359</v>
+        <v>130108130</v>
       </c>
       <c r="B83" t="n">
         <v>79180</v>
@@ -10070,16 +10056,19 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>507226</v>
+        <v>506954</v>
       </c>
       <c r="R83" t="n">
-        <v>7032851</v>
+        <v>7033030</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10114,19 +10103,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10250,45 +10250,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130107347</v>
+        <v>130107309</v>
       </c>
       <c r="B85" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>507473</v>
+        <v>507227</v>
       </c>
       <c r="R85" t="n">
-        <v>7032872</v>
+        <v>7032981</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10325,7 +10332,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en sälg i granskog.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10334,8 +10341,34 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10352,10 +10385,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130107349</v>
+        <v>130108122</v>
       </c>
       <c r="B86" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10363,34 +10396,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>507397</v>
+        <v>506980</v>
       </c>
       <c r="R86" t="n">
-        <v>7032912</v>
+        <v>7032966</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10427,7 +10468,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10438,6 +10479,26 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10454,52 +10515,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130107309</v>
+        <v>130107349</v>
       </c>
       <c r="B87" t="n">
-        <v>80314</v>
+        <v>79180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>507227</v>
+        <v>507397</v>
       </c>
       <c r="R87" t="n">
-        <v>7032981</v>
+        <v>7032912</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10536,7 +10590,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På en sälg i granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10545,34 +10599,8 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10705,10 +10733,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130108122</v>
+        <v>130107347</v>
       </c>
       <c r="B89" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10716,42 +10744,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506980</v>
+        <v>507473</v>
       </c>
       <c r="R89" t="n">
-        <v>7032966</v>
+        <v>7032872</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10788,7 +10808,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10799,26 +10819,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130108119</v>
+        <v>130107373</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,42 +1859,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506988</v>
+        <v>507202</v>
       </c>
       <c r="R12" t="n">
-        <v>7032934</v>
+        <v>7033195</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,7 +1923,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,26 +1934,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2113,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107373</v>
+        <v>130108119</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,34 +2096,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507202</v>
+        <v>506988</v>
       </c>
       <c r="R14" t="n">
-        <v>7033195</v>
+        <v>7032934</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,7 +2168,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,6 +2179,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130108113</v>
+        <v>130107305</v>
       </c>
       <c r="B32" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,26 +4172,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4199,10 +4204,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507086</v>
+        <v>507427</v>
       </c>
       <c r="R32" t="n">
-        <v>7032654</v>
+        <v>7032906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4237,16 +4242,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4257,9 +4271,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4379,10 +4398,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107305</v>
+        <v>130108113</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4390,31 +4409,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4422,10 +4436,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507427</v>
+        <v>507086</v>
       </c>
       <c r="R34" t="n">
-        <v>7032906</v>
+        <v>7032654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4460,25 +4474,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4489,14 +4494,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5891,49 +5891,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107312</v>
+        <v>130107362</v>
       </c>
       <c r="B47" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507337</v>
+        <v>507201</v>
       </c>
       <c r="R47" t="n">
-        <v>7032943</v>
+        <v>7032984</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5968,20 +5964,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5998,7 +5993,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107362</v>
+        <v>130107365</v>
       </c>
       <c r="B48" t="n">
         <v>79180</v>
@@ -6033,10 +6028,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507201</v>
+        <v>507106</v>
       </c>
       <c r="R48" t="n">
-        <v>7032984</v>
+        <v>7033205</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6073,7 +6068,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6100,7 +6095,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130107365</v>
+        <v>130107368</v>
       </c>
       <c r="B49" t="n">
         <v>79180</v>
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507106</v>
+        <v>507204</v>
       </c>
       <c r="R49" t="n">
-        <v>7033205</v>
+        <v>7033154</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6175,7 +6170,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6202,45 +6197,52 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107368</v>
+        <v>130107327</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>80321</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507204</v>
+        <v>507239</v>
       </c>
       <c r="R50" t="n">
-        <v>7033154</v>
+        <v>7032943</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6277,7 +6279,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6286,8 +6288,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6304,41 +6327,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107327</v>
+        <v>130107310</v>
       </c>
       <c r="B51" t="n">
-        <v>80321</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6346,10 +6366,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507239</v>
+        <v>507084</v>
       </c>
       <c r="R51" t="n">
-        <v>7032943</v>
+        <v>7033149</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6386,7 +6406,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6395,7 +6415,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6406,17 +6425,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6434,38 +6458,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107310</v>
+        <v>130107312</v>
       </c>
       <c r="B52" t="n">
-        <v>57823</v>
+        <v>97791</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6473,10 +6497,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507084</v>
+        <v>507337</v>
       </c>
       <c r="R52" t="n">
-        <v>7033149</v>
+        <v>7032943</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6511,43 +6535,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6811,45 +6811,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107336</v>
+        <v>130107318</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507081</v>
+        <v>507226</v>
       </c>
       <c r="R55" t="n">
-        <v>7032660</v>
+        <v>7033130</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6884,19 +6888,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6913,10 +6918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130107352</v>
+        <v>130108124</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6924,34 +6929,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507537</v>
+        <v>506973</v>
       </c>
       <c r="R56" t="n">
-        <v>7032882</v>
+        <v>7032980</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6988,7 +7001,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6999,6 +7012,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7015,10 +7048,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130108124</v>
+        <v>130107336</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7026,42 +7059,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506973</v>
+        <v>507081</v>
       </c>
       <c r="R57" t="n">
-        <v>7032980</v>
+        <v>7032660</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,7 +7123,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7109,26 +7134,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7145,49 +7150,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130107318</v>
+        <v>130107352</v>
       </c>
       <c r="B58" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507226</v>
+        <v>507537</v>
       </c>
       <c r="R58" t="n">
-        <v>7033130</v>
+        <v>7032882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7222,20 +7223,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7470,7 +7470,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130107367</v>
+        <v>130107335</v>
       </c>
       <c r="B61" t="n">
         <v>79180</v>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507157</v>
+        <v>507088</v>
       </c>
       <c r="R61" t="n">
-        <v>7033174</v>
+        <v>7032634</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107335</v>
+        <v>130107325</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,34 +7583,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507088</v>
+        <v>507225</v>
       </c>
       <c r="R62" t="n">
-        <v>7032634</v>
+        <v>7033115</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7647,7 +7650,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7656,8 +7659,34 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7674,10 +7703,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130107325</v>
+        <v>130107303</v>
       </c>
       <c r="B63" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7685,26 +7714,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7712,10 +7746,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507225</v>
+        <v>507345</v>
       </c>
       <c r="R63" t="n">
-        <v>7033115</v>
+        <v>7032953</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7752,7 +7786,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7761,7 +7795,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7772,22 +7805,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7805,7 +7838,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130107303</v>
+        <v>130108118</v>
       </c>
       <c r="B64" t="n">
         <v>57826</v>
@@ -7838,7 +7871,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7848,10 +7881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507345</v>
+        <v>506992</v>
       </c>
       <c r="R64" t="n">
-        <v>7032953</v>
+        <v>7032926</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7888,7 +7921,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7902,7 +7935,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -7915,14 +7948,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7940,10 +7968,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130108118</v>
+        <v>130107367</v>
       </c>
       <c r="B65" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7951,42 +7979,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506992</v>
+        <v>507157</v>
       </c>
       <c r="R65" t="n">
-        <v>7032926</v>
+        <v>7033174</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8023,7 +8043,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8034,26 +8054,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130107351</v>
+        <v>130108123</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8821,34 +8821,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507466</v>
+        <v>506984</v>
       </c>
       <c r="R72" t="n">
-        <v>7032900</v>
+        <v>7032983</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8885,7 +8893,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8896,6 +8904,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8912,7 +8940,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130107340</v>
+        <v>130107351</v>
       </c>
       <c r="B73" t="n">
         <v>79180</v>
@@ -8947,10 +8975,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507241</v>
+        <v>507466</v>
       </c>
       <c r="R73" t="n">
-        <v>7032773</v>
+        <v>7032900</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8987,7 +9015,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9014,10 +9042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130108123</v>
+        <v>130107340</v>
       </c>
       <c r="B74" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9025,42 +9053,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506984</v>
+        <v>507241</v>
       </c>
       <c r="R74" t="n">
-        <v>7032983</v>
+        <v>7032773</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9097,7 +9117,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9108,26 +9128,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9795,10 +9795,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130107348</v>
+        <v>130108121</v>
       </c>
       <c r="B81" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9806,34 +9806,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>507432</v>
+        <v>506981</v>
       </c>
       <c r="R81" t="n">
-        <v>7032888</v>
+        <v>7032960</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9870,7 +9878,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9881,6 +9889,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9897,7 +9925,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130108130</v>
+        <v>130107348</v>
       </c>
       <c r="B82" t="n">
         <v>79180</v>
@@ -9926,19 +9954,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506954</v>
+        <v>507432</v>
       </c>
       <c r="R82" t="n">
-        <v>7033030</v>
+        <v>7032888</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9973,30 +9998,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10013,10 +10027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130108121</v>
+        <v>130108130</v>
       </c>
       <c r="B83" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,31 +10038,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10056,10 +10065,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506981</v>
+        <v>506954</v>
       </c>
       <c r="R83" t="n">
-        <v>7032960</v>
+        <v>7033030</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10094,24 +10103,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -10250,10 +10250,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130108122</v>
+        <v>130107349</v>
       </c>
       <c r="B85" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10261,42 +10261,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506980</v>
+        <v>507397</v>
       </c>
       <c r="R85" t="n">
-        <v>7032966</v>
+        <v>7032912</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10333,7 +10325,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10344,26 +10336,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10380,7 +10352,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130107349</v>
+        <v>130107347</v>
       </c>
       <c r="B86" t="n">
         <v>79180</v>
@@ -10415,10 +10387,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>507397</v>
+        <v>507473</v>
       </c>
       <c r="R86" t="n">
-        <v>7032912</v>
+        <v>7032872</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10482,45 +10454,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130107347</v>
+        <v>130107309</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>507473</v>
+        <v>507227</v>
       </c>
       <c r="R87" t="n">
-        <v>7032872</v>
+        <v>7032981</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10557,7 +10536,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en sälg i granskog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10566,8 +10545,34 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10584,10 +10589,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130108114</v>
+        <v>130108122</v>
       </c>
       <c r="B88" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10595,26 +10600,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10622,10 +10632,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>507064</v>
+        <v>506980</v>
       </c>
       <c r="R88" t="n">
-        <v>7032974</v>
+        <v>7032966</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10660,15 +10670,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -10700,41 +10719,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130107309</v>
+        <v>130108114</v>
       </c>
       <c r="B89" t="n">
-        <v>80314</v>
+        <v>83158</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10742,10 +10757,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507227</v>
+        <v>507064</v>
       </c>
       <c r="R89" t="n">
-        <v>7032981</v>
+        <v>7032974</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10780,11 +10795,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På en sälg i granskog.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10795,29 +10805,19 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130107373</v>
+        <v>130108119</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,34 +1859,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507202</v>
+        <v>506988</v>
       </c>
       <c r="R12" t="n">
-        <v>7033195</v>
+        <v>7032934</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,7 +1931,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,6 +1942,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2085,10 +2113,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130108119</v>
+        <v>130107373</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,42 +2124,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506988</v>
+        <v>507202</v>
       </c>
       <c r="R14" t="n">
-        <v>7032934</v>
+        <v>7033195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2188,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,26 +2199,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -3569,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130108126</v>
+        <v>130107366</v>
       </c>
       <c r="B27" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,50 +3580,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507059</v>
+        <v>507149</v>
       </c>
       <c r="R27" t="n">
-        <v>7032796</v>
+        <v>7033155</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3658,6 +3642,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3666,11 +3655,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3687,10 +3671,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130108127</v>
+        <v>130108115</v>
       </c>
       <c r="B28" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3698,21 +3682,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3725,10 +3709,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507051</v>
+        <v>506966</v>
       </c>
       <c r="R28" t="n">
-        <v>7032835</v>
+        <v>7032974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3773,24 +3757,19 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3808,41 +3787,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107326</v>
+        <v>130108127</v>
       </c>
       <c r="B29" t="n">
-        <v>80321</v>
+        <v>80285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3850,10 +3825,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507353</v>
+        <v>507051</v>
       </c>
       <c r="R29" t="n">
-        <v>7032907</v>
+        <v>7032835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3888,11 +3863,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3918,14 +3888,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3943,37 +3908,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130108115</v>
+        <v>130107326</v>
       </c>
       <c r="B30" t="n">
-        <v>83158</v>
+        <v>80321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3981,10 +3950,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506966</v>
+        <v>507353</v>
       </c>
       <c r="R30" t="n">
-        <v>7032974</v>
+        <v>7032907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4019,6 +3988,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4029,19 +4003,29 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4059,10 +4043,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4070,34 +4054,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R31" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,11 +4132,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4145,6 +4140,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107305</v>
+        <v>130108113</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,31 +4172,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4204,10 +4199,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507427</v>
+        <v>507086</v>
       </c>
       <c r="R32" t="n">
-        <v>7032906</v>
+        <v>7032654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4242,25 +4237,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4271,14 +4257,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4398,10 +4379,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130108113</v>
+        <v>130107305</v>
       </c>
       <c r="B34" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,26 +4390,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4436,10 +4422,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507086</v>
+        <v>507427</v>
       </c>
       <c r="R34" t="n">
-        <v>7032654</v>
+        <v>7032906</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4474,16 +4460,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4494,9 +4489,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107339</v>
+        <v>130107332</v>
       </c>
       <c r="B36" t="n">
         <v>79180</v>
@@ -4650,19 +4650,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507154</v>
+        <v>507011</v>
       </c>
       <c r="R36" t="n">
-        <v>7032764</v>
+        <v>7033080</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4699,7 +4696,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På en stående död granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4708,34 +4705,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4752,7 +4723,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107370</v>
+        <v>130107339</v>
       </c>
       <c r="B37" t="n">
         <v>79180</v>
@@ -4790,10 +4761,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507211</v>
+        <v>507154</v>
       </c>
       <c r="R37" t="n">
-        <v>7033009</v>
+        <v>7032764</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4830,7 +4801,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På en stående död granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4860,12 +4831,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4883,7 +4854,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107332</v>
+        <v>130107370</v>
       </c>
       <c r="B38" t="n">
         <v>79180</v>
@@ -4912,16 +4883,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507011</v>
+        <v>507211</v>
       </c>
       <c r="R38" t="n">
-        <v>7033080</v>
+        <v>7033009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4958,7 +4932,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4967,8 +4941,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5891,45 +5891,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107362</v>
+        <v>130107312</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507201</v>
+        <v>507337</v>
       </c>
       <c r="R47" t="n">
-        <v>7032984</v>
+        <v>7032943</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5964,19 +5968,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5993,7 +5998,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107365</v>
+        <v>130107362</v>
       </c>
       <c r="B48" t="n">
         <v>79180</v>
@@ -6028,10 +6033,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507106</v>
+        <v>507201</v>
       </c>
       <c r="R48" t="n">
-        <v>7033205</v>
+        <v>7032984</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6068,7 +6073,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6095,7 +6100,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130107368</v>
+        <v>130107365</v>
       </c>
       <c r="B49" t="n">
         <v>79180</v>
@@ -6130,10 +6135,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507204</v>
+        <v>507106</v>
       </c>
       <c r="R49" t="n">
-        <v>7033154</v>
+        <v>7033205</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6170,7 +6175,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6197,52 +6202,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107327</v>
+        <v>130107368</v>
       </c>
       <c r="B50" t="n">
-        <v>80321</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507239</v>
+        <v>507204</v>
       </c>
       <c r="R50" t="n">
-        <v>7032943</v>
+        <v>7033154</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6279,7 +6277,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6288,29 +6286,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6327,38 +6304,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107310</v>
+        <v>130107327</v>
       </c>
       <c r="B51" t="n">
-        <v>57823</v>
+        <v>80321</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6366,10 +6346,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507084</v>
+        <v>507239</v>
       </c>
       <c r="R51" t="n">
-        <v>7033149</v>
+        <v>7032943</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6406,7 +6386,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6415,6 +6395,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6425,22 +6406,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6458,38 +6434,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107312</v>
+        <v>130107310</v>
       </c>
       <c r="B52" t="n">
-        <v>97791</v>
+        <v>57823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6497,10 +6473,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507337</v>
+        <v>507084</v>
       </c>
       <c r="R52" t="n">
-        <v>7032943</v>
+        <v>7033149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6535,19 +6511,43 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6811,49 +6811,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107318</v>
+        <v>130107336</v>
       </c>
       <c r="B55" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507226</v>
+        <v>507081</v>
       </c>
       <c r="R55" t="n">
-        <v>7033130</v>
+        <v>7032660</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6888,20 +6884,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6918,10 +6913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130108124</v>
+        <v>130107352</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,42 +6924,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506973</v>
+        <v>507537</v>
       </c>
       <c r="R56" t="n">
-        <v>7032980</v>
+        <v>7032882</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7001,7 +6988,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7012,26 +6999,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7048,10 +7015,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130107336</v>
+        <v>130108124</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7059,34 +7026,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507081</v>
+        <v>506973</v>
       </c>
       <c r="R57" t="n">
-        <v>7032660</v>
+        <v>7032980</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7123,7 +7098,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7134,6 +7109,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7150,45 +7145,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130107352</v>
+        <v>130107318</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507537</v>
+        <v>507226</v>
       </c>
       <c r="R58" t="n">
-        <v>7032882</v>
+        <v>7033130</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7223,19 +7222,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7470,7 +7470,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130107335</v>
+        <v>130107367</v>
       </c>
       <c r="B61" t="n">
         <v>79180</v>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507088</v>
+        <v>507157</v>
       </c>
       <c r="R61" t="n">
-        <v>7032634</v>
+        <v>7033174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107325</v>
+        <v>130107335</v>
       </c>
       <c r="B62" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,37 +7583,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507225</v>
+        <v>507088</v>
       </c>
       <c r="R62" t="n">
-        <v>7033115</v>
+        <v>7032634</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7650,7 +7647,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7659,34 +7656,8 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7703,10 +7674,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130107303</v>
+        <v>130107325</v>
       </c>
       <c r="B63" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7714,31 +7685,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7746,10 +7712,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507345</v>
+        <v>507225</v>
       </c>
       <c r="R63" t="n">
-        <v>7032953</v>
+        <v>7033115</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7786,7 +7752,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7795,6 +7761,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7805,22 +7772,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7838,7 +7805,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130108118</v>
+        <v>130107303</v>
       </c>
       <c r="B64" t="n">
         <v>57826</v>
@@ -7871,7 +7838,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7881,10 +7848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506992</v>
+        <v>507345</v>
       </c>
       <c r="R64" t="n">
-        <v>7032926</v>
+        <v>7032953</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7921,7 +7888,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7935,7 +7902,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -7948,9 +7915,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7968,10 +7940,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130107367</v>
+        <v>130108118</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7979,34 +7951,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507157</v>
+        <v>506992</v>
       </c>
       <c r="R65" t="n">
-        <v>7033174</v>
+        <v>7032926</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8043,7 +8023,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8054,6 +8034,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130108123</v>
+        <v>130107351</v>
       </c>
       <c r="B72" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8821,42 +8821,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506984</v>
+        <v>507466</v>
       </c>
       <c r="R72" t="n">
-        <v>7032983</v>
+        <v>7032900</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8893,7 +8885,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8904,26 +8896,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8940,7 +8912,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130107351</v>
+        <v>130107340</v>
       </c>
       <c r="B73" t="n">
         <v>79180</v>
@@ -8975,10 +8947,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507466</v>
+        <v>507241</v>
       </c>
       <c r="R73" t="n">
-        <v>7032900</v>
+        <v>7032773</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9015,7 +8987,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9042,10 +9014,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130107340</v>
+        <v>130108123</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9053,34 +9025,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507241</v>
+        <v>506984</v>
       </c>
       <c r="R74" t="n">
-        <v>7032773</v>
+        <v>7032983</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9117,7 +9097,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9128,6 +9108,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9358,10 +9358,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130107331</v>
+        <v>130107333</v>
       </c>
       <c r="B77" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9369,37 +9369,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507157</v>
+        <v>507097</v>
       </c>
       <c r="R77" t="n">
-        <v>7033090</v>
+        <v>7032620</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9436,7 +9433,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9445,34 +9442,8 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9489,10 +9460,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130107333</v>
+        <v>130107331</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9500,34 +9471,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507097</v>
+        <v>507157</v>
       </c>
       <c r="R78" t="n">
-        <v>7032620</v>
+        <v>7033090</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9564,7 +9538,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9573,8 +9547,34 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9795,10 +9795,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130108121</v>
+        <v>130107348</v>
       </c>
       <c r="B81" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9806,42 +9806,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506981</v>
+        <v>507432</v>
       </c>
       <c r="R81" t="n">
-        <v>7032960</v>
+        <v>7032888</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9878,7 +9870,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gammal gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9889,26 +9881,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9925,7 +9897,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130107348</v>
+        <v>130108130</v>
       </c>
       <c r="B82" t="n">
         <v>79180</v>
@@ -9954,16 +9926,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>507432</v>
+        <v>506954</v>
       </c>
       <c r="R82" t="n">
-        <v>7032888</v>
+        <v>7033030</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9998,19 +9973,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10027,10 +10013,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130108130</v>
+        <v>130108121</v>
       </c>
       <c r="B83" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10038,26 +10024,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10065,10 +10056,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506954</v>
+        <v>506981</v>
       </c>
       <c r="R83" t="n">
-        <v>7033030</v>
+        <v>7032960</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10103,15 +10094,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -10250,10 +10250,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130107349</v>
+        <v>130108122</v>
       </c>
       <c r="B85" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10261,34 +10261,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>507397</v>
+        <v>506980</v>
       </c>
       <c r="R85" t="n">
-        <v>7032912</v>
+        <v>7032966</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10325,7 +10333,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10336,6 +10344,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10352,7 +10380,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130107347</v>
+        <v>130107349</v>
       </c>
       <c r="B86" t="n">
         <v>79180</v>
@@ -10387,10 +10415,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>507473</v>
+        <v>507397</v>
       </c>
       <c r="R86" t="n">
-        <v>7032872</v>
+        <v>7032912</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10454,52 +10482,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130107309</v>
+        <v>130107347</v>
       </c>
       <c r="B87" t="n">
-        <v>80314</v>
+        <v>79180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>507227</v>
+        <v>507473</v>
       </c>
       <c r="R87" t="n">
-        <v>7032981</v>
+        <v>7032872</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10536,7 +10557,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På en sälg i granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10545,34 +10566,8 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10589,10 +10584,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130108122</v>
+        <v>130108114</v>
       </c>
       <c r="B88" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10600,31 +10595,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10632,10 +10622,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506980</v>
+        <v>507064</v>
       </c>
       <c r="R88" t="n">
-        <v>7032966</v>
+        <v>7032974</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10670,24 +10660,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -10719,37 +10700,41 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130108114</v>
+        <v>130107309</v>
       </c>
       <c r="B89" t="n">
-        <v>83158</v>
+        <v>80314</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10757,10 +10742,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507064</v>
+        <v>507227</v>
       </c>
       <c r="R89" t="n">
-        <v>7032974</v>
+        <v>7032981</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10795,6 +10780,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På en sälg i granskog.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10805,19 +10795,29 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107316</v>
+        <v>130107338</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507075</v>
+        <v>507073</v>
       </c>
       <c r="R2" t="n">
-        <v>7033179</v>
+        <v>7032765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,20 +748,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107338</v>
+        <v>130107321</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507073</v>
+        <v>507522</v>
       </c>
       <c r="R3" t="n">
-        <v>7032765</v>
+        <v>7032834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +855,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,8 +864,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1019,37 +1043,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107321</v>
+        <v>130107316</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>97791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507522</v>
+        <v>507075</v>
       </c>
       <c r="R5" t="n">
-        <v>7032834</v>
+        <v>7033179</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,11 +1120,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1112,27 +1132,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,34 +3580,50 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R27" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,11 +3658,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3655,6 +3666,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3671,10 +3687,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130108115</v>
+        <v>130108127</v>
       </c>
       <c r="B28" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3682,21 +3698,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3709,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506966</v>
+        <v>507051</v>
       </c>
       <c r="R28" t="n">
-        <v>7032974</v>
+        <v>7032835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,19 +3773,24 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3787,37 +3808,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130108127</v>
+        <v>130107326</v>
       </c>
       <c r="B29" t="n">
-        <v>80285</v>
+        <v>80321</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3825,10 +3850,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507051</v>
+        <v>507353</v>
       </c>
       <c r="R29" t="n">
-        <v>7032835</v>
+        <v>7032907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3863,6 +3888,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3888,9 +3918,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3908,41 +3943,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107326</v>
+        <v>130108115</v>
       </c>
       <c r="B30" t="n">
-        <v>80321</v>
+        <v>83158</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3950,10 +3981,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507353</v>
+        <v>506966</v>
       </c>
       <c r="R30" t="n">
-        <v>7032907</v>
+        <v>7032974</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3988,11 +4019,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4003,29 +4029,19 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4043,10 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130108126</v>
+        <v>130107366</v>
       </c>
       <c r="B31" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4054,50 +4070,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507059</v>
+        <v>507149</v>
       </c>
       <c r="R31" t="n">
-        <v>7032796</v>
+        <v>7033155</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,6 +4132,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4140,11 +4145,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130108113</v>
+        <v>130107305</v>
       </c>
       <c r="B32" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,26 +4172,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4199,10 +4204,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507086</v>
+        <v>507427</v>
       </c>
       <c r="R32" t="n">
-        <v>7032654</v>
+        <v>7032906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4237,16 +4242,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4257,9 +4271,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4379,10 +4398,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107305</v>
+        <v>130108113</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4390,31 +4409,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4422,10 +4436,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507427</v>
+        <v>507086</v>
       </c>
       <c r="R34" t="n">
-        <v>7032906</v>
+        <v>7032654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4460,25 +4474,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4489,14 +4494,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107332</v>
+        <v>130107339</v>
       </c>
       <c r="B36" t="n">
         <v>79180</v>
@@ -4650,16 +4650,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507011</v>
+        <v>507154</v>
       </c>
       <c r="R36" t="n">
-        <v>7033080</v>
+        <v>7032764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4696,7 +4699,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en stående död granhögstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4705,8 +4708,34 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4723,7 +4752,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107339</v>
+        <v>130107370</v>
       </c>
       <c r="B37" t="n">
         <v>79180</v>
@@ -4761,10 +4790,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507154</v>
+        <v>507211</v>
       </c>
       <c r="R37" t="n">
-        <v>7032764</v>
+        <v>7033009</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4801,7 +4830,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På en stående död granhögstubbe.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4831,12 +4860,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4854,7 +4883,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107370</v>
+        <v>130107332</v>
       </c>
       <c r="B38" t="n">
         <v>79180</v>
@@ -4883,19 +4912,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507211</v>
+        <v>507011</v>
       </c>
       <c r="R38" t="n">
-        <v>7033009</v>
+        <v>7033080</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4932,7 +4958,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4941,34 +4967,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -6811,45 +6811,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107336</v>
+        <v>130107318</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507081</v>
+        <v>507226</v>
       </c>
       <c r="R55" t="n">
-        <v>7032660</v>
+        <v>7033130</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6884,19 +6888,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6913,10 +6918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130107352</v>
+        <v>130108124</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6924,34 +6929,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507537</v>
+        <v>506973</v>
       </c>
       <c r="R56" t="n">
-        <v>7032882</v>
+        <v>7032980</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6988,7 +7001,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6999,6 +7012,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7015,10 +7048,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130108124</v>
+        <v>130107336</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7026,42 +7059,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506973</v>
+        <v>507081</v>
       </c>
       <c r="R57" t="n">
-        <v>7032980</v>
+        <v>7032660</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,7 +7123,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7109,26 +7134,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7145,49 +7150,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130107318</v>
+        <v>130107352</v>
       </c>
       <c r="B58" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507226</v>
+        <v>507537</v>
       </c>
       <c r="R58" t="n">
-        <v>7033130</v>
+        <v>7032882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7222,20 +7223,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107338</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107321</v>
+        <v>130108125</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,26 +788,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507522</v>
+        <v>506976</v>
       </c>
       <c r="R3" t="n">
-        <v>7032834</v>
+        <v>7032983</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +860,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,33 +869,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130108125</v>
+        <v>130107321</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,31 +923,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506976</v>
+        <v>507522</v>
       </c>
       <c r="R4" t="n">
-        <v>7032983</v>
+        <v>7032834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +999,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
         <v>130107316</v>
       </c>
       <c r="B5" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>130107354</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107371</v>
+        <v>130107360</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,16 +1281,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507222</v>
+        <v>507211</v>
       </c>
       <c r="R7" t="n">
-        <v>7033039</v>
+        <v>7032876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1330,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,8 +1339,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1354,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107341</v>
+        <v>130107371</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507330</v>
+        <v>507222</v>
       </c>
       <c r="R8" t="n">
-        <v>7032840</v>
+        <v>7033039</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107360</v>
+        <v>130107341</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,19 +1514,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507211</v>
+        <v>507330</v>
       </c>
       <c r="R9" t="n">
-        <v>7032876</v>
+        <v>7032840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1560,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,34 +1569,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107322</v>
+        <v>130108117</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,26 +1598,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1625,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507355</v>
+        <v>507057</v>
       </c>
       <c r="R10" t="n">
-        <v>7032906</v>
+        <v>7032982</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1670,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,33 +1679,27 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1718,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130108117</v>
+        <v>130107322</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,31 +1728,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1761,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507057</v>
+        <v>507355</v>
       </c>
       <c r="R11" t="n">
-        <v>7032982</v>
+        <v>7032906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,27 +1804,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130108119</v>
+        <v>130107373</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,42 +1859,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506988</v>
+        <v>507202</v>
       </c>
       <c r="R12" t="n">
-        <v>7032934</v>
+        <v>7033195</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,7 +1923,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,26 +1934,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2113,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107373</v>
+        <v>130108119</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,34 +2096,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507202</v>
+        <v>506988</v>
       </c>
       <c r="R14" t="n">
-        <v>7033195</v>
+        <v>7032934</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,7 +2168,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,6 +2179,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2215,10 +2215,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107369</v>
+        <v>130107323</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,34 +2226,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507237</v>
+        <v>507416</v>
       </c>
       <c r="R15" t="n">
-        <v>7033036</v>
+        <v>7032925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2290,7 +2293,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,8 +2302,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2317,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107363</v>
+        <v>130107369</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,10 +2381,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507069</v>
+        <v>507237</v>
       </c>
       <c r="R16" t="n">
-        <v>7033199</v>
+        <v>7033036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,10 +2448,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130108131</v>
+        <v>130107363</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,19 +2477,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506958</v>
+        <v>507069</v>
       </c>
       <c r="R17" t="n">
-        <v>7032984</v>
+        <v>7033199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,30 +2521,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2535,10 +2550,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130107374</v>
+        <v>130108131</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2564,16 +2579,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507101</v>
+        <v>506958</v>
       </c>
       <c r="R18" t="n">
-        <v>7033240</v>
+        <v>7032984</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,19 +2626,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gran i granskog.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2637,10 +2666,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130107353</v>
+        <v>130107374</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507521</v>
+        <v>507101</v>
       </c>
       <c r="R19" t="n">
-        <v>7032767</v>
+        <v>7033240</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,7 +2741,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107345</v>
+        <v>130107353</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507468</v>
+        <v>507521</v>
       </c>
       <c r="R20" t="n">
-        <v>7032839</v>
+        <v>7032767</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,10 +2870,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107323</v>
+        <v>130107345</v>
       </c>
       <c r="B21" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2852,37 +2881,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507416</v>
+        <v>507468</v>
       </c>
       <c r="R21" t="n">
-        <v>7032925</v>
+        <v>7032839</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2945,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,34 +2954,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2972,48 +2972,61 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107361</v>
+        <v>130107328</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>57930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507236</v>
+        <v>507190</v>
       </c>
       <c r="R22" t="n">
-        <v>7032990</v>
+        <v>7033178</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3050,7 +3063,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,33 +3072,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3106,7 +3098,7 @@
         <v>130107355</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,7 +3200,7 @@
         <v>130107356</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3307,10 +3299,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107307</v>
+        <v>130107361</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,46 +3310,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507225</v>
+        <v>507236</v>
       </c>
       <c r="R25" t="n">
-        <v>7033149</v>
+        <v>7032990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3377,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3403,6 +3386,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3423,12 +3407,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3446,27 +3430,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107328</v>
+        <v>130107307</v>
       </c>
       <c r="B26" t="n">
-        <v>57930</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3474,16 +3458,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3497,10 +3477,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507190</v>
+        <v>507225</v>
       </c>
       <c r="R26" t="n">
-        <v>7033178</v>
+        <v>7033149</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3517,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3552,6 +3532,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130108126</v>
+        <v>130108127</v>
       </c>
       <c r="B27" t="n">
-        <v>57985</v>
+        <v>80288</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,50 +3580,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507059</v>
+        <v>507051</v>
       </c>
       <c r="R27" t="n">
-        <v>7032796</v>
+        <v>7032835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3664,12 +3651,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3687,37 +3690,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130108127</v>
+        <v>130107326</v>
       </c>
       <c r="B28" t="n">
-        <v>80285</v>
+        <v>80324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3725,10 +3732,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507051</v>
+        <v>507353</v>
       </c>
       <c r="R28" t="n">
-        <v>7032835</v>
+        <v>7032907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3763,6 +3770,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3788,9 +3800,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3808,52 +3825,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107326</v>
+        <v>130107366</v>
       </c>
       <c r="B29" t="n">
-        <v>80321</v>
+        <v>79183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507353</v>
+        <v>507149</v>
       </c>
       <c r="R29" t="n">
-        <v>7032907</v>
+        <v>7033155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3890,7 +3900,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3899,34 +3909,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3946,7 +3930,7 @@
         <v>130108115</v>
       </c>
       <c r="B30" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4059,10 +4043,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4070,34 +4054,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R31" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,11 +4132,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4145,6 +4140,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107305</v>
+        <v>130107350</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,42 +4172,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507427</v>
+        <v>507429</v>
       </c>
       <c r="R32" t="n">
-        <v>7032906</v>
+        <v>7032901</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4244,7 +4236,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,31 +4247,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4296,10 +4263,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130107350</v>
+        <v>130108113</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>83161</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,34 +4274,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507429</v>
+        <v>507086</v>
       </c>
       <c r="R33" t="n">
-        <v>7032901</v>
+        <v>7032654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4369,19 +4339,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4398,10 +4379,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130108113</v>
+        <v>130107305</v>
       </c>
       <c r="B34" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,26 +4390,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4436,10 +4422,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507086</v>
+        <v>507427</v>
       </c>
       <c r="R34" t="n">
-        <v>7032654</v>
+        <v>7032906</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4474,16 +4460,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4494,9 +4489,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4517,7 +4517,7 @@
         <v>130107317</v>
       </c>
       <c r="B35" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>130107339</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107370</v>
+        <v>130107332</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4781,19 +4781,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507211</v>
+        <v>507011</v>
       </c>
       <c r="R37" t="n">
-        <v>7033009</v>
+        <v>7033080</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4830,7 +4827,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4839,34 +4836,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4883,10 +4854,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107332</v>
+        <v>130107370</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4912,16 +4883,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507011</v>
+        <v>507211</v>
       </c>
       <c r="R38" t="n">
-        <v>7033080</v>
+        <v>7033009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4958,7 +4932,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4967,8 +4941,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4988,7 +4988,7 @@
         <v>130107329</v>
       </c>
       <c r="B39" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>130107343</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>130107342</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>130107357</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>130107364</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>130107311</v>
       </c>
       <c r="B44" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>130108129</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>130107324</v>
       </c>
       <c r="B46" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5891,38 +5891,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107312</v>
+        <v>130108128</v>
       </c>
       <c r="B47" t="n">
-        <v>97791</v>
+        <v>78195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5930,10 +5929,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507337</v>
+        <v>507058</v>
       </c>
       <c r="R47" t="n">
-        <v>7032943</v>
+        <v>7032972</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5978,9 +5977,19 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5998,45 +6007,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107362</v>
+        <v>130107327</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>80324</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507201</v>
+        <v>507239</v>
       </c>
       <c r="R48" t="n">
-        <v>7032984</v>
+        <v>7032943</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6073,7 +6089,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6082,8 +6098,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6100,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130107365</v>
+        <v>130107310</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6111,34 +6148,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507106</v>
+        <v>507084</v>
       </c>
       <c r="R49" t="n">
-        <v>7033205</v>
+        <v>7033149</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6175,7 +6216,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6186,6 +6227,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6202,45 +6268,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107368</v>
+        <v>130107312</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>97794</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507204</v>
+        <v>507337</v>
       </c>
       <c r="R50" t="n">
-        <v>7033154</v>
+        <v>7032943</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6275,19 +6345,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6304,52 +6375,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107327</v>
+        <v>130107362</v>
       </c>
       <c r="B51" t="n">
-        <v>80321</v>
+        <v>79183</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507239</v>
+        <v>507201</v>
       </c>
       <c r="R51" t="n">
-        <v>7032943</v>
+        <v>7032984</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6386,7 +6450,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6395,29 +6459,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6434,10 +6477,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107310</v>
+        <v>130107365</v>
       </c>
       <c r="B52" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6445,38 +6488,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507084</v>
+        <v>507106</v>
       </c>
       <c r="R52" t="n">
-        <v>7033149</v>
+        <v>7033205</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6513,7 +6552,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6524,31 +6563,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6565,10 +6579,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130108128</v>
+        <v>130107368</v>
       </c>
       <c r="B53" t="n">
-        <v>78192</v>
+        <v>79183</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6576,37 +6590,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507058</v>
+        <v>507204</v>
       </c>
       <c r="R53" t="n">
-        <v>7032972</v>
+        <v>7033154</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6641,30 +6652,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6814,7 +6814,7 @@
         <v>130107318</v>
       </c>
       <c r="B55" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130108124</v>
+        <v>130107358</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,42 +6929,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506973</v>
+        <v>507233</v>
       </c>
       <c r="R56" t="n">
-        <v>7032980</v>
+        <v>7032821</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7001,7 +6993,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7012,26 +7004,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7051,7 +7023,7 @@
         <v>130107336</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7153,7 +7125,7 @@
         <v>130107352</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7255,7 +7227,7 @@
         <v>130108116</v>
       </c>
       <c r="B59" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7368,10 +7340,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130107358</v>
+        <v>130108124</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7379,34 +7351,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507233</v>
+        <v>506973</v>
       </c>
       <c r="R60" t="n">
-        <v>7032821</v>
+        <v>7032980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7443,7 +7423,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7454,6 +7434,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7473,7 +7473,7 @@
         <v>130107367</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7572,10 +7572,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107335</v>
+        <v>130107330</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,34 +7583,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507088</v>
+        <v>507223</v>
       </c>
       <c r="R62" t="n">
-        <v>7032634</v>
+        <v>7032791</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7647,7 +7650,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7656,8 +7659,34 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7674,10 +7703,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130107325</v>
+        <v>130107335</v>
       </c>
       <c r="B63" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7685,37 +7714,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507225</v>
+        <v>507088</v>
       </c>
       <c r="R63" t="n">
-        <v>7033115</v>
+        <v>7032634</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7752,7 +7778,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7761,34 +7787,8 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7805,7 +7805,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130107303</v>
+        <v>130108118</v>
       </c>
       <c r="B64" t="n">
         <v>57826</v>
@@ -7838,7 +7838,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7848,10 +7848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507345</v>
+        <v>506992</v>
       </c>
       <c r="R64" t="n">
-        <v>7032953</v>
+        <v>7032926</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -7915,14 +7915,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7940,10 +7935,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130108118</v>
+        <v>130107325</v>
       </c>
       <c r="B65" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7951,31 +7946,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7983,10 +7973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506992</v>
+        <v>507225</v>
       </c>
       <c r="R65" t="n">
-        <v>7032926</v>
+        <v>7033115</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8023,7 +8013,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8032,27 +8022,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8070,10 +8066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130107330</v>
+        <v>130107303</v>
       </c>
       <c r="B66" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8081,24 +8077,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8108,10 +8109,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507223</v>
+        <v>507345</v>
       </c>
       <c r="R66" t="n">
-        <v>7032791</v>
+        <v>7032953</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8148,7 +8149,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8157,7 +8158,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8204,7 +8204,7 @@
         <v>130107337</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>130107372</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>130107344</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>130107351</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>130107340</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>130107314</v>
       </c>
       <c r="B75" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>130107315</v>
       </c>
       <c r="B76" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9358,10 +9358,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130107333</v>
+        <v>130107331</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9369,34 +9369,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507097</v>
+        <v>507157</v>
       </c>
       <c r="R77" t="n">
-        <v>7032620</v>
+        <v>7033090</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9433,7 +9436,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9442,8 +9445,34 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9460,10 +9489,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130107331</v>
+        <v>130107333</v>
       </c>
       <c r="B78" t="n">
-        <v>91748</v>
+        <v>79183</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9471,37 +9500,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507157</v>
+        <v>507097</v>
       </c>
       <c r="R78" t="n">
-        <v>7033090</v>
+        <v>7032620</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9538,7 +9564,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9547,34 +9573,8 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9591,45 +9591,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130107359</v>
+        <v>130107313</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>97794</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507226</v>
+        <v>507399</v>
       </c>
       <c r="R79" t="n">
-        <v>7032851</v>
+        <v>7032831</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9664,19 +9668,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9693,10 +9698,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130107346</v>
+        <v>130107359</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9728,10 +9733,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>507521</v>
+        <v>507226</v>
       </c>
       <c r="R80" t="n">
-        <v>7032862</v>
+        <v>7032851</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9768,7 +9773,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9795,10 +9800,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130107348</v>
+        <v>130107346</v>
       </c>
       <c r="B81" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9830,10 +9835,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>507432</v>
+        <v>507521</v>
       </c>
       <c r="R81" t="n">
-        <v>7032888</v>
+        <v>7032862</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9870,7 +9875,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9897,10 +9902,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130108130</v>
+        <v>130107348</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9926,19 +9931,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506954</v>
+        <v>507432</v>
       </c>
       <c r="R82" t="n">
-        <v>7033030</v>
+        <v>7032888</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9973,30 +9975,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10013,10 +10004,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130108121</v>
+        <v>130108130</v>
       </c>
       <c r="B83" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10024,31 +10015,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10056,10 +10042,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506981</v>
+        <v>506954</v>
       </c>
       <c r="R83" t="n">
-        <v>7032960</v>
+        <v>7033030</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10094,24 +10080,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -10143,38 +10120,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130107313</v>
+        <v>130108121</v>
       </c>
       <c r="B84" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10182,10 +10163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>507399</v>
+        <v>506981</v>
       </c>
       <c r="R84" t="n">
-        <v>7032831</v>
+        <v>7032960</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10220,19 +10201,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10250,10 +10250,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130108122</v>
+        <v>130107349</v>
       </c>
       <c r="B85" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10261,42 +10261,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506980</v>
+        <v>507397</v>
       </c>
       <c r="R85" t="n">
-        <v>7032966</v>
+        <v>7032912</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10333,7 +10325,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10344,26 +10336,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10380,10 +10352,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130107349</v>
+        <v>130108114</v>
       </c>
       <c r="B86" t="n">
-        <v>79180</v>
+        <v>83161</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10391,34 +10363,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>507397</v>
+        <v>507064</v>
       </c>
       <c r="R86" t="n">
-        <v>7032912</v>
+        <v>7032974</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10453,19 +10428,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10485,7 +10471,7 @@
         <v>130107347</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10584,10 +10570,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130108114</v>
+        <v>130108122</v>
       </c>
       <c r="B88" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10595,26 +10581,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10622,10 +10613,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>507064</v>
+        <v>506980</v>
       </c>
       <c r="R88" t="n">
-        <v>7032974</v>
+        <v>7032966</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10660,15 +10651,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>130107309</v>
       </c>
       <c r="B89" t="n">
-        <v>80314</v>
+        <v>80317</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>130107319</v>
       </c>
       <c r="B90" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107338</v>
+        <v>130107329</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507073</v>
+        <v>507152</v>
       </c>
       <c r="R2" t="n">
-        <v>7032765</v>
+        <v>7033148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,8 +766,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,53 +810,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130108125</v>
+        <v>130107332</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506976</v>
+        <v>507011</v>
       </c>
       <c r="R3" t="n">
-        <v>7032983</v>
+        <v>7033080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,31 +896,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,48 +912,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107321</v>
+        <v>130107333</v>
       </c>
       <c r="B4" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507522</v>
+        <v>507097</v>
       </c>
       <c r="R4" t="n">
-        <v>7032834</v>
+        <v>7032620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,34 +996,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1043,49 +1014,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107316</v>
+        <v>130107335</v>
       </c>
       <c r="B5" t="n">
-        <v>97794</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507075</v>
+        <v>507088</v>
       </c>
       <c r="R5" t="n">
-        <v>7033179</v>
+        <v>7032634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,20 +1087,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1150,14 +1116,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130107354</v>
+        <v>130107336</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1185,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507440</v>
+        <v>507081</v>
       </c>
       <c r="R6" t="n">
-        <v>7032815</v>
+        <v>7032660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1191,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,14 +1218,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107360</v>
+        <v>130107337</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1281,19 +1247,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507211</v>
+        <v>507084</v>
       </c>
       <c r="R7" t="n">
-        <v>7032876</v>
+        <v>7032690</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1293,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,34 +1302,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1383,14 +1320,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107371</v>
+        <v>130107338</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1418,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507222</v>
+        <v>507073</v>
       </c>
       <c r="R8" t="n">
-        <v>7033039</v>
+        <v>7032765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1395,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,14 +1422,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107341</v>
+        <v>130107339</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1514,16 +1451,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507330</v>
+        <v>507154</v>
       </c>
       <c r="R9" t="n">
-        <v>7032840</v>
+        <v>7032764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,7 +1500,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en stående död granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,8 +1509,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1587,53 +1553,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130108117</v>
+        <v>130107340</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507057</v>
+        <v>507241</v>
       </c>
       <c r="R10" t="n">
-        <v>7032982</v>
+        <v>7032773</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1628,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,26 +1639,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1717,48 +1655,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107322</v>
+        <v>130107341</v>
       </c>
       <c r="B11" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507355</v>
+        <v>507330</v>
       </c>
       <c r="R11" t="n">
-        <v>7032906</v>
+        <v>7032840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1730,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,34 +1739,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1848,14 +1757,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130107373</v>
+        <v>130107342</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1883,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507202</v>
+        <v>507376</v>
       </c>
       <c r="R12" t="n">
-        <v>7033195</v>
+        <v>7032813</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,7 +1832,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,53 +1859,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107304</v>
+        <v>130107343</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507441</v>
+        <v>507356</v>
       </c>
       <c r="R13" t="n">
-        <v>7032908</v>
+        <v>7032842</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +1934,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,31 +1945,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2085,42 +1961,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130108119</v>
+        <v>130107344</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2128,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506988</v>
+        <v>507358</v>
       </c>
       <c r="R14" t="n">
-        <v>7032934</v>
+        <v>7032855</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,12 +2048,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2195,9 +2067,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2215,48 +2092,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107323</v>
+        <v>130107345</v>
       </c>
       <c r="B15" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507416</v>
+        <v>507468</v>
       </c>
       <c r="R15" t="n">
-        <v>7032925</v>
+        <v>7032839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2167,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,34 +2176,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2346,14 +2194,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107369</v>
+        <v>130107346</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2381,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507237</v>
+        <v>507521</v>
       </c>
       <c r="R16" t="n">
-        <v>7033036</v>
+        <v>7032862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2421,7 +2269,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2448,14 +2296,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107363</v>
+        <v>130107347</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2483,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507069</v>
+        <v>507473</v>
       </c>
       <c r="R17" t="n">
-        <v>7033199</v>
+        <v>7032872</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2550,14 +2398,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108131</v>
+        <v>130107348</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2579,19 +2427,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506958</v>
+        <v>507432</v>
       </c>
       <c r="R18" t="n">
-        <v>7032984</v>
+        <v>7032888</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,30 +2471,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2666,14 +2500,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130107374</v>
+        <v>130107349</v>
       </c>
       <c r="B19" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2701,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507101</v>
+        <v>507397</v>
       </c>
       <c r="R19" t="n">
-        <v>7033240</v>
+        <v>7032912</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2741,7 +2575,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,14 +2602,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107353</v>
+        <v>130107350</v>
       </c>
       <c r="B20" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2803,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507521</v>
+        <v>507429</v>
       </c>
       <c r="R20" t="n">
-        <v>7032767</v>
+        <v>7032901</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2843,7 +2677,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,14 +2704,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107345</v>
+        <v>130107351</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2905,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507468</v>
+        <v>507466</v>
       </c>
       <c r="R21" t="n">
-        <v>7032839</v>
+        <v>7032900</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2779,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,61 +2806,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107328</v>
+        <v>130107352</v>
       </c>
       <c r="B22" t="n">
-        <v>57930</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507190</v>
+        <v>507537</v>
       </c>
       <c r="R22" t="n">
-        <v>7033178</v>
+        <v>7032882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3063,7 +2881,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,11 +2892,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3095,14 +2908,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107355</v>
+        <v>130107353</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3130,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507422</v>
+        <v>507521</v>
       </c>
       <c r="R23" t="n">
-        <v>7032836</v>
+        <v>7032767</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3197,14 +3010,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107356</v>
+        <v>130107354</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3232,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507326</v>
+        <v>507440</v>
       </c>
       <c r="R24" t="n">
-        <v>7032797</v>
+        <v>7032815</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3299,14 +3112,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107361</v>
+        <v>130107355</v>
       </c>
       <c r="B25" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3328,19 +3141,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507236</v>
+        <v>507422</v>
       </c>
       <c r="R25" t="n">
-        <v>7032990</v>
+        <v>7032836</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3377,7 +3187,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,34 +3196,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3430,57 +3214,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107307</v>
+        <v>130107356</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507225</v>
+        <v>507326</v>
       </c>
       <c r="R26" t="n">
-        <v>7033149</v>
+        <v>7032797</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,7 +3289,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,31 +3300,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3569,48 +3316,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130108127</v>
+        <v>130107357</v>
       </c>
       <c r="B27" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507051</v>
+        <v>507283</v>
       </c>
       <c r="R27" t="n">
-        <v>7032835</v>
+        <v>7032795</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3645,35 +3389,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3690,52 +3418,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107326</v>
+        <v>130107358</v>
       </c>
       <c r="B28" t="n">
-        <v>80324</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507353</v>
+        <v>507233</v>
       </c>
       <c r="R28" t="n">
-        <v>7032907</v>
+        <v>7032821</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3772,7 +3493,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3781,34 +3502,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3825,14 +3520,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107366</v>
+        <v>130107359</v>
       </c>
       <c r="B29" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3860,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507149</v>
+        <v>507226</v>
       </c>
       <c r="R29" t="n">
-        <v>7033155</v>
+        <v>7032851</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3927,32 +3622,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130108115</v>
+        <v>130107360</v>
       </c>
       <c r="B30" t="n">
-        <v>83161</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,10 +3660,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506966</v>
+        <v>507211</v>
       </c>
       <c r="R30" t="n">
-        <v>7032974</v>
+        <v>7032876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4003,6 +3698,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4013,6 +3713,11 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4023,9 +3728,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4043,61 +3753,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130108126</v>
+        <v>130107361</v>
       </c>
       <c r="B31" t="n">
-        <v>57985</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507059</v>
+        <v>507236</v>
       </c>
       <c r="R31" t="n">
-        <v>7032796</v>
+        <v>7032990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,18 +3829,44 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4161,14 +3884,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107350</v>
+        <v>130107362</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4196,10 +3919,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507429</v>
+        <v>507201</v>
       </c>
       <c r="R32" t="n">
-        <v>7032901</v>
+        <v>7032984</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4236,7 +3959,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4263,48 +3986,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130108113</v>
+        <v>130107363</v>
       </c>
       <c r="B33" t="n">
-        <v>83161</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507086</v>
+        <v>507069</v>
       </c>
       <c r="R33" t="n">
-        <v>7032654</v>
+        <v>7033199</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4339,30 +4059,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4379,53 +4088,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107305</v>
+        <v>130107364</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507427</v>
+        <v>507091</v>
       </c>
       <c r="R34" t="n">
-        <v>7032906</v>
+        <v>7033218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4462,7 +4163,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4473,31 +4174,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4514,49 +4190,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107317</v>
+        <v>130107365</v>
       </c>
       <c r="B35" t="n">
-        <v>97794</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507267</v>
+        <v>507106</v>
       </c>
       <c r="R35" t="n">
-        <v>7033117</v>
+        <v>7033205</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4591,20 +4263,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4621,14 +4292,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107339</v>
+        <v>130107366</v>
       </c>
       <c r="B36" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4650,19 +4321,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507154</v>
+        <v>507149</v>
       </c>
       <c r="R36" t="n">
-        <v>7032764</v>
+        <v>7033155</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4699,7 +4367,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På en stående död granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4708,34 +4376,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4752,14 +4394,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107332</v>
+        <v>130107367</v>
       </c>
       <c r="B37" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4787,10 +4429,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507011</v>
+        <v>507157</v>
       </c>
       <c r="R37" t="n">
-        <v>7033080</v>
+        <v>7033174</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4827,7 +4469,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4854,14 +4496,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107370</v>
+        <v>130107368</v>
       </c>
       <c r="B38" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4883,19 +4525,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507211</v>
+        <v>507204</v>
       </c>
       <c r="R38" t="n">
-        <v>7033009</v>
+        <v>7033154</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4932,7 +4571,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4941,34 +4580,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4985,52 +4598,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107329</v>
+        <v>130107369</v>
       </c>
       <c r="B39" t="n">
-        <v>91727</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507152</v>
+        <v>507237</v>
       </c>
       <c r="R39" t="n">
-        <v>7033148</v>
+        <v>7033036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5067,7 +4673,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5076,34 +4682,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5120,14 +4700,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130107343</v>
+        <v>130107370</v>
       </c>
       <c r="B40" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5149,16 +4729,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507356</v>
+        <v>507211</v>
       </c>
       <c r="R40" t="n">
-        <v>7032842</v>
+        <v>7033009</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5195,7 +4778,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,8 +4787,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5222,14 +4831,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107342</v>
+        <v>130107371</v>
       </c>
       <c r="B41" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5257,10 +4866,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507376</v>
+        <v>507222</v>
       </c>
       <c r="R41" t="n">
-        <v>7032813</v>
+        <v>7033039</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5324,14 +4933,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107357</v>
+        <v>130107372</v>
       </c>
       <c r="B42" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5359,10 +4968,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507283</v>
+        <v>507223</v>
       </c>
       <c r="R42" t="n">
-        <v>7032795</v>
+        <v>7033198</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5399,7 +5008,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5426,14 +5035,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130107364</v>
+        <v>130107373</v>
       </c>
       <c r="B43" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5461,10 +5070,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507091</v>
+        <v>507202</v>
       </c>
       <c r="R43" t="n">
-        <v>7033218</v>
+        <v>7033195</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5501,7 +5110,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5528,49 +5137,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107311</v>
+        <v>130107374</v>
       </c>
       <c r="B44" t="n">
-        <v>97794</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507355</v>
+        <v>507101</v>
       </c>
       <c r="R44" t="n">
-        <v>7032851</v>
+        <v>7033240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,20 +5210,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5638,11 +5242,11 @@
         <v>130108129</v>
       </c>
       <c r="B45" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5756,41 +5360,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130107324</v>
+        <v>130108130</v>
       </c>
       <c r="B46" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5798,10 +5398,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507238</v>
+        <v>506954</v>
       </c>
       <c r="R46" t="n">
-        <v>7032941</v>
+        <v>7033030</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5836,11 +5436,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5851,29 +5446,19 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5891,32 +5476,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130108128</v>
+        <v>130108131</v>
       </c>
       <c r="B47" t="n">
-        <v>78195</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5929,10 +5514,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507058</v>
+        <v>506958</v>
       </c>
       <c r="R47" t="n">
-        <v>7032972</v>
+        <v>7032984</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6007,41 +5592,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130107327</v>
+        <v>130108113</v>
       </c>
       <c r="B48" t="n">
-        <v>80324</v>
+        <v>83307</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6049,10 +5630,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507239</v>
+        <v>507086</v>
       </c>
       <c r="R48" t="n">
-        <v>7032943</v>
+        <v>7032654</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6087,11 +5668,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6102,24 +5678,19 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6137,10 +5708,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130107310</v>
+        <v>130108114</v>
       </c>
       <c r="B49" t="n">
-        <v>57823</v>
+        <v>83307</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,27 +5719,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6176,10 +5746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507084</v>
+        <v>507064</v>
       </c>
       <c r="R49" t="n">
-        <v>7033149</v>
+        <v>7032974</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6214,25 +5784,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6243,14 +5804,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6268,38 +5824,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107312</v>
+        <v>130108115</v>
       </c>
       <c r="B50" t="n">
-        <v>97794</v>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6307,10 +5862,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507337</v>
+        <v>506966</v>
       </c>
       <c r="R50" t="n">
-        <v>7032943</v>
+        <v>7032974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6355,9 +5910,19 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6375,10 +5940,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107362</v>
+        <v>130108116</v>
       </c>
       <c r="B51" t="n">
-        <v>79183</v>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6386,31 +5951,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507201</v>
+        <v>506959</v>
       </c>
       <c r="R51" t="n">
         <v>7032984</v>
@@ -6448,19 +6016,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6477,10 +6056,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107365</v>
+        <v>130107321</v>
       </c>
       <c r="B52" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6488,34 +6067,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507106</v>
+        <v>507522</v>
       </c>
       <c r="R52" t="n">
-        <v>7033205</v>
+        <v>7032834</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6552,7 +6134,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6561,8 +6143,34 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6579,10 +6187,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130107368</v>
+        <v>130107322</v>
       </c>
       <c r="B53" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6590,34 +6198,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507204</v>
+        <v>507355</v>
       </c>
       <c r="R53" t="n">
-        <v>7033154</v>
+        <v>7032906</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6654,7 +6265,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6663,8 +6274,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6681,10 +6318,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130108120</v>
+        <v>130107323</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6692,31 +6329,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6724,10 +6356,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506983</v>
+        <v>507416</v>
       </c>
       <c r="R54" t="n">
-        <v>7032942</v>
+        <v>7032925</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6764,7 +6396,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6773,27 +6405,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6811,38 +6449,41 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130107318</v>
+        <v>130107324</v>
       </c>
       <c r="B55" t="n">
-        <v>97794</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6850,10 +6491,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507226</v>
+        <v>507238</v>
       </c>
       <c r="R55" t="n">
-        <v>7033130</v>
+        <v>7032941</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6888,6 +6529,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6901,6 +6547,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6918,10 +6584,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130107358</v>
+        <v>130107325</v>
       </c>
       <c r="B56" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,34 +6595,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507233</v>
+        <v>507225</v>
       </c>
       <c r="R56" t="n">
-        <v>7032821</v>
+        <v>7033115</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6993,7 +6662,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7002,8 +6671,34 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7020,10 +6715,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130107336</v>
+        <v>130108127</v>
       </c>
       <c r="B57" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7031,34 +6726,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507081</v>
+        <v>507051</v>
       </c>
       <c r="R57" t="n">
-        <v>7032660</v>
+        <v>7032835</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7093,19 +6791,35 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7122,45 +6836,52 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130107352</v>
+        <v>130107309</v>
       </c>
       <c r="B58" t="n">
-        <v>79183</v>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507537</v>
+        <v>507227</v>
       </c>
       <c r="R58" t="n">
-        <v>7032882</v>
+        <v>7032981</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7197,7 +6918,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en sälg i granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7206,8 +6927,34 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7224,37 +6971,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130108116</v>
+        <v>130107326</v>
       </c>
       <c r="B59" t="n">
-        <v>83161</v>
+        <v>80468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7262,10 +7013,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506959</v>
+        <v>507353</v>
       </c>
       <c r="R59" t="n">
-        <v>7032984</v>
+        <v>7032907</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7300,6 +7051,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7310,19 +7066,29 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7340,40 +7106,39 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130108124</v>
+        <v>130107327</v>
       </c>
       <c r="B60" t="n">
-        <v>57826</v>
+        <v>80468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7383,10 +7148,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506973</v>
+        <v>507239</v>
       </c>
       <c r="R60" t="n">
-        <v>7032980</v>
+        <v>7032943</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7423,7 +7188,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7432,27 +7197,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7470,45 +7236,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130107367</v>
+        <v>130107310</v>
       </c>
       <c r="B61" t="n">
-        <v>79183</v>
+        <v>57950</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507157</v>
+        <v>507084</v>
       </c>
       <c r="R61" t="n">
-        <v>7033174</v>
+        <v>7033149</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7545,7 +7315,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7556,6 +7326,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7572,10 +7367,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130107330</v>
+        <v>130107302</v>
       </c>
       <c r="B62" t="n">
-        <v>91751</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,24 +7378,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7610,10 +7410,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507223</v>
+        <v>507075</v>
       </c>
       <c r="R62" t="n">
-        <v>7032791</v>
+        <v>7032759</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7650,7 +7450,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7659,7 +7459,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7703,10 +7502,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130107335</v>
+        <v>130107303</v>
       </c>
       <c r="B63" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7714,34 +7513,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507088</v>
+        <v>507345</v>
       </c>
       <c r="R63" t="n">
-        <v>7032634</v>
+        <v>7032953</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7778,7 +7585,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7789,6 +7596,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7805,10 +7637,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130108118</v>
+        <v>130107304</v>
       </c>
       <c r="B64" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7838,7 +7670,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7848,10 +7680,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506992</v>
+        <v>507441</v>
       </c>
       <c r="R64" t="n">
-        <v>7032926</v>
+        <v>7032908</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7888,7 +7720,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7902,7 +7734,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -7915,9 +7747,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7935,10 +7772,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130107325</v>
+        <v>130107305</v>
       </c>
       <c r="B65" t="n">
-        <v>80288</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7946,26 +7783,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7973,10 +7815,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507225</v>
+        <v>507427</v>
       </c>
       <c r="R65" t="n">
-        <v>7033115</v>
+        <v>7032906</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8013,7 +7855,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8022,7 +7864,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8033,22 +7874,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8066,10 +7907,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130107303</v>
+        <v>130107306</v>
       </c>
       <c r="B66" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8099,20 +7940,24 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507345</v>
+        <v>507221</v>
       </c>
       <c r="R66" t="n">
-        <v>7032953</v>
+        <v>7033159</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8149,7 +7994,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8201,10 +8046,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130107337</v>
+        <v>130107307</v>
       </c>
       <c r="B67" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8212,34 +8057,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507084</v>
+        <v>507225</v>
       </c>
       <c r="R67" t="n">
-        <v>7032690</v>
+        <v>7033149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8276,7 +8133,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8287,6 +8144,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8303,10 +8185,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130107372</v>
+        <v>130108117</v>
       </c>
       <c r="B68" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8314,34 +8196,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507223</v>
+        <v>507057</v>
       </c>
       <c r="R68" t="n">
-        <v>7033198</v>
+        <v>7032982</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8378,7 +8268,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8389,6 +8279,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8405,10 +8315,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130107344</v>
+        <v>130108118</v>
       </c>
       <c r="B69" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8416,26 +8326,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8443,10 +8358,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507358</v>
+        <v>506992</v>
       </c>
       <c r="R69" t="n">
-        <v>7032855</v>
+        <v>7032926</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8483,7 +8398,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8492,13 +8407,12 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -8511,14 +8425,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8536,10 +8445,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130107306</v>
+        <v>130108119</v>
       </c>
       <c r="B70" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8569,24 +8478,20 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507221</v>
+        <v>506988</v>
       </c>
       <c r="R70" t="n">
-        <v>7033159</v>
+        <v>7032934</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8623,7 +8528,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8637,7 +8542,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -8650,14 +8555,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8675,10 +8575,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130107302</v>
+        <v>130108120</v>
       </c>
       <c r="B71" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8718,10 +8618,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507075</v>
+        <v>506983</v>
       </c>
       <c r="R71" t="n">
-        <v>7032759</v>
+        <v>7032942</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8758,7 +8658,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8772,7 +8672,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -8785,14 +8685,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8810,10 +8705,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130107351</v>
+        <v>130108121</v>
       </c>
       <c r="B72" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8821,34 +8716,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507466</v>
+        <v>506981</v>
       </c>
       <c r="R72" t="n">
-        <v>7032900</v>
+        <v>7032960</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8885,7 +8788,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8896,6 +8799,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8912,10 +8835,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130107340</v>
+        <v>130108122</v>
       </c>
       <c r="B73" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8923,34 +8846,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507241</v>
+        <v>506980</v>
       </c>
       <c r="R73" t="n">
-        <v>7032773</v>
+        <v>7032966</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8987,7 +8918,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8998,6 +8929,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9017,7 +8968,7 @@
         <v>130108123</v>
       </c>
       <c r="B74" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9144,38 +9095,42 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130107314</v>
+        <v>130108124</v>
       </c>
       <c r="B75" t="n">
-        <v>97794</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9183,10 +9138,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507176</v>
+        <v>506973</v>
       </c>
       <c r="R75" t="n">
-        <v>7032962</v>
+        <v>7032980</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9221,19 +9176,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9251,38 +9225,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130107315</v>
+        <v>130108125</v>
       </c>
       <c r="B76" t="n">
-        <v>97794</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9290,10 +9268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507217</v>
+        <v>506976</v>
       </c>
       <c r="R76" t="n">
-        <v>7033002</v>
+        <v>7032983</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9328,19 +9306,43 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9358,10 +9360,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130107331</v>
+        <v>130108126</v>
       </c>
       <c r="B77" t="n">
-        <v>91751</v>
+        <v>58114</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9369,37 +9371,50 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507157</v>
+        <v>507059</v>
       </c>
       <c r="R77" t="n">
-        <v>7033090</v>
+        <v>7032796</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9434,44 +9449,18 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9489,10 +9478,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130107333</v>
+        <v>130107328</v>
       </c>
       <c r="B78" t="n">
-        <v>79183</v>
+        <v>58057</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9500,34 +9489,50 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507097</v>
+        <v>507190</v>
       </c>
       <c r="R78" t="n">
-        <v>7032620</v>
+        <v>7033178</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9564,7 +9569,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9575,6 +9580,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9591,10 +9601,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130107313</v>
+        <v>130107311</v>
       </c>
       <c r="B79" t="n">
-        <v>97794</v>
+        <v>97983</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9630,10 +9640,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507399</v>
+        <v>507355</v>
       </c>
       <c r="R79" t="n">
-        <v>7032831</v>
+        <v>7032851</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9698,45 +9708,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130107359</v>
+        <v>130107312</v>
       </c>
       <c r="B80" t="n">
-        <v>79183</v>
+        <v>97983</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>507226</v>
+        <v>507337</v>
       </c>
       <c r="R80" t="n">
-        <v>7032851</v>
+        <v>7032943</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9771,19 +9785,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9800,45 +9815,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130107346</v>
+        <v>130107313</v>
       </c>
       <c r="B81" t="n">
-        <v>79183</v>
+        <v>97983</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>507521</v>
+        <v>507399</v>
       </c>
       <c r="R81" t="n">
-        <v>7032862</v>
+        <v>7032831</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9873,19 +9892,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9902,45 +9922,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130107348</v>
+        <v>130107314</v>
       </c>
       <c r="B82" t="n">
-        <v>79183</v>
+        <v>97983</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>507432</v>
+        <v>507176</v>
       </c>
       <c r="R82" t="n">
-        <v>7032888</v>
+        <v>7032962</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9975,19 +9999,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10004,37 +10029,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130108130</v>
+        <v>130107315</v>
       </c>
       <c r="B83" t="n">
-        <v>79183</v>
+        <v>97983</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10042,10 +10068,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506954</v>
+        <v>507217</v>
       </c>
       <c r="R83" t="n">
-        <v>7033030</v>
+        <v>7033002</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10090,19 +10116,9 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10120,42 +10136,38 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130108121</v>
+        <v>130107316</v>
       </c>
       <c r="B84" t="n">
-        <v>57826</v>
+        <v>97983</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10163,10 +10175,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506981</v>
+        <v>507075</v>
       </c>
       <c r="R84" t="n">
-        <v>7032960</v>
+        <v>7033179</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10201,38 +10213,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10250,45 +10243,49 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130107349</v>
+        <v>130107317</v>
       </c>
       <c r="B85" t="n">
-        <v>79183</v>
+        <v>97983</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>507397</v>
+        <v>507267</v>
       </c>
       <c r="R85" t="n">
-        <v>7032912</v>
+        <v>7033117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10323,19 +10320,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10352,37 +10350,38 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130108114</v>
+        <v>130107318</v>
       </c>
       <c r="B86" t="n">
-        <v>83161</v>
+        <v>97983</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10390,10 +10389,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>507064</v>
+        <v>507226</v>
       </c>
       <c r="R86" t="n">
-        <v>7032974</v>
+        <v>7033130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10438,19 +10437,9 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10468,45 +10457,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130107347</v>
+        <v>130107319</v>
       </c>
       <c r="B87" t="n">
-        <v>79183</v>
+        <v>97983</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>507473</v>
+        <v>507144</v>
       </c>
       <c r="R87" t="n">
-        <v>7032872</v>
+        <v>7033068</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10541,19 +10534,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10570,10 +10564,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130108122</v>
+        <v>130108128</v>
       </c>
       <c r="B88" t="n">
-        <v>57826</v>
+        <v>78339</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10581,31 +10575,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10613,10 +10602,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506980</v>
+        <v>507058</v>
       </c>
       <c r="R88" t="n">
-        <v>7032966</v>
+        <v>7032972</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10651,24 +10640,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -10697,248 +10677,6 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>130107309</v>
-      </c>
-      <c r="B89" t="n">
-        <v>80317</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Getsjöflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>507227</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7032981</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Häggenås</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På en sälg i granskog.</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF89" t="inlineStr"/>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>130107319</v>
-      </c>
-      <c r="B90" t="n">
-        <v>97794</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Getsjöflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>507144</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7033068</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Häggenås</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF90" t="inlineStr"/>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56899-2025 artfynd.xlsx
+++ b/artfynd/A 56899-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107333</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107335</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107336</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107337</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107338</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107339</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107340</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107341</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1856,6 +1911,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107342</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107343</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107344</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2191,6 +2261,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107345</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2293,6 +2368,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107346</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2395,6 +2475,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107347</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2497,6 +2582,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107348</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2599,6 +2689,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107349</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2701,6 +2796,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107350</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2803,6 +2903,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107351</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2905,6 +3010,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107352</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3007,6 +3117,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107353</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3109,6 +3224,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107354</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3211,6 +3331,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107355</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3313,6 +3438,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107356</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3415,6 +3545,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107357</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3517,6 +3652,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107358</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3619,6 +3759,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107359</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3750,6 +3895,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107360</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3881,6 +4031,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107361</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3983,6 +4138,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107362</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4085,6 +4245,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107363</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4187,6 +4352,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107364</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4289,6 +4459,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107365</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4391,6 +4566,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107366</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4493,6 +4673,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107367</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4595,6 +4780,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107368</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4697,6 +4887,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107369</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4828,6 +5023,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107370</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4930,6 +5130,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107371</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5032,6 +5237,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107372</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5134,6 +5344,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107373</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5236,6 +5451,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107374</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5357,6 +5577,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108129</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5473,6 +5698,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108130</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5589,6 +5819,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108131</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5705,6 +5940,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108113</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5821,6 +6061,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108114</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5937,6 +6182,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108115</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6053,6 +6303,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108116</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6184,6 +6439,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107321</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6315,6 +6575,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107322</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6446,6 +6711,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107323</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6581,6 +6851,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107324</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6712,6 +6987,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107325</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6833,6 +7113,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108127</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6968,6 +7253,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107309</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7103,6 +7393,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107326</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7233,6 +7528,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107327</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7364,6 +7664,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107310</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7499,6 +7804,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107302</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7634,6 +7944,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107303</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7769,6 +8084,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107304</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7904,6 +8224,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107305</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8043,6 +8368,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107306</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8182,6 +8512,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107307</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8312,6 +8647,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108117</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8442,6 +8782,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108118</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8572,6 +8917,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108119</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8702,6 +9052,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108120</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8832,6 +9187,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108121</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8962,6 +9322,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108122</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9092,6 +9457,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108123</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9222,6 +9592,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108124</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9357,6 +9732,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108125</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9475,6 +9855,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108126</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9598,6 +9983,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107328</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9705,6 +10095,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107311</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9812,6 +10207,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107312</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9919,6 +10319,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107313</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10026,6 +10431,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107314</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10133,6 +10543,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107315</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10240,6 +10655,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107316</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10347,6 +10767,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107317</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10454,6 +10879,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107318</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10561,6 +10991,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107319</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10677,8 +11112,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108128</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>